--- a/noodlepy/data/Biofluid_list_annotated_v4.xlsx
+++ b/noodlepy/data/Biofluid_list_annotated_v4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Victor\Documents\ML Spectroscopy Code\Combined Spectroscopy Updated\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yifeigu/Documents/Carney_Lab/NoodlePy/noodlepy/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51C2987-5049-40DA-B7D4-621B141B348F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED8611D-07BC-D248-BCB5-4BE474D4C10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34080" yWindow="500" windowWidth="30240" windowHeight="18880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="22">
   <si>
     <t>OD Number</t>
   </si>
@@ -73,9 +73,6 @@
   </si>
   <si>
     <t>Gender</t>
-  </si>
-  <si>
-    <t>Race/Ethnicity</t>
   </si>
   <si>
     <t>BMI</t>
@@ -121,6 +118,12 @@
   </si>
   <si>
     <t>G_stage</t>
+  </si>
+  <si>
+    <t>Race</t>
+  </si>
+  <si>
+    <t>American Indian or Alaska Native</t>
   </si>
 </sst>
 </file>
@@ -192,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -209,6 +212,13 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -229,9 +239,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -269,7 +279,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -375,7 +385,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -517,7 +527,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -526,13 +536,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S219"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.796875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12" style="2" customWidth="1"/>
-    <col min="4" max="5" width="11" style="2"/>
-    <col min="6" max="6" width="27.796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.5" style="2" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="2" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="0" style="2" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="2"/>
+    <col min="6" max="6" width="27.83203125" style="2" customWidth="1"/>
     <col min="7" max="7" width="11" style="2"/>
     <col min="8" max="8" width="18.5" style="2" customWidth="1"/>
     <col min="9" max="14" width="11" style="2"/>
@@ -540,7 +551,7 @@
     <col min="16" max="16384" width="11" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -557,81 +568,50 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
-        <v>272</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2">
-        <v>73</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>166</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="2">
-        <v>27.1</v>
+        <v>10</v>
       </c>
       <c r="H2" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2">
         <v>1</v>
       </c>
       <c r="J2" s="2" cm="1">
         <f t="array" ref="J2">_xlfn.IFS(H2=0,0,H2=1,1,H2=2,1,H2=3,2,H2=4,2)</f>
-        <v>2</v>
-      </c>
-      <c r="K2" s="2">
-        <f>COUNTIF(H2:H102,0)</f>
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="O2" s="4"/>
       <c r="S2" s="4"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
-        <v>275</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2">
-        <v>86</v>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>191</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="2">
-        <v>25.58</v>
+        <v>10</v>
       </c>
       <c r="H3" s="2">
         <v>4</v>
@@ -643,291 +623,295 @@
         <f t="array" ref="J3">_xlfn.IFS(H3=0,0,H3=1,1,H3=2,1,H3=3,2,H3=4,2)</f>
         <v>2</v>
       </c>
-      <c r="K3" s="2">
-        <f>COUNTIF(H2:H102,1)</f>
-        <v>17</v>
-      </c>
       <c r="O3" s="4"/>
       <c r="S3" s="4"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4" s="2">
-        <v>32.31</v>
+        <v>27.1</v>
       </c>
       <c r="H4" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
       </c>
       <c r="J4" s="2" cm="1">
         <f t="array" ref="J4">_xlfn.IFS(H4=0,0,H4=1,1,H4=2,1,H4=3,2,H4=4,2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="2">
-        <f>COUNTIF(H2:H102,2)</f>
-        <v>12</v>
+        <f>COUNTIF(H4:H104,0)</f>
+        <v>35</v>
       </c>
       <c r="O4" s="4"/>
       <c r="S4" s="4"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" s="2">
-        <v>26.38</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
+        <v>25.58</v>
+      </c>
+      <c r="H5" s="2">
+        <v>4</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" cm="1">
         <f t="array" ref="J5">_xlfn.IFS(H5=0,0,H5=1,1,H5=2,1,H5=3,2,H5=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="2">
-        <f>COUNTIF(H2:H102,3)</f>
-        <v>7</v>
+        <f>COUNTIF(H4:H104,1)</f>
+        <v>17</v>
       </c>
       <c r="O5" s="4"/>
       <c r="S5" s="4"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6" s="2">
-        <v>20.14</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0</v>
+        <v>32.31</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2" cm="1">
         <f t="array" ref="J6">_xlfn.IFS(H6=0,0,H6=1,1,H6=2,1,H6=3,2,H6=4,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2">
-        <f>COUNTIF(H2:H102,4)</f>
-        <v>30</v>
+        <f>COUNTIF(H4:H104,2)</f>
+        <v>12</v>
       </c>
       <c r="O6" s="4"/>
       <c r="S6" s="4"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="2">
-        <v>31.51</v>
+        <v>26.38</v>
       </c>
       <c r="H7" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" cm="1">
         <f t="array" ref="J7">_xlfn.IFS(H7=0,0,H7=1,1,H7=2,1,H7=3,2,H7=4,2)</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <f>COUNTIF(H4:H104,3)</f>
+        <v>7</v>
       </c>
       <c r="O7" s="4"/>
       <c r="S7" s="4"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8" s="2">
-        <v>21.34</v>
+        <v>20.14</v>
       </c>
       <c r="H8" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" cm="1">
         <f t="array" ref="J8">_xlfn.IFS(H8=0,0,H8=1,1,H8=2,1,H8=3,2,H8=4,2)</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <f>COUNTIF(H4:H104,4)</f>
+        <v>30</v>
       </c>
       <c r="O8" s="4"/>
       <c r="S8" s="4"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G9" s="2">
-        <v>30.41</v>
+        <v>31.51</v>
       </c>
       <c r="H9" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="2" cm="1">
         <f t="array" ref="J9">_xlfn.IFS(H9=0,0,H9=1,1,H9=2,1,H9=3,2,H9=4,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="4"/>
       <c r="S9" s="4"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G10" s="2">
-        <v>23.74</v>
+        <v>21.34</v>
       </c>
       <c r="H10" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10" s="2">
         <v>1</v>
       </c>
       <c r="J10" s="2" cm="1">
         <f t="array" ref="J10">_xlfn.IFS(H10=0,0,H10=1,1,H10=2,1,H10=3,2,H10=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" s="4"/>
       <c r="S10" s="4"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" s="2">
-        <v>23.59</v>
+        <v>30.41</v>
       </c>
       <c r="H11" s="5">
         <v>0</v>
@@ -942,30 +926,30 @@
       <c r="O11" s="4"/>
       <c r="S11" s="4"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G12" s="2">
-        <v>26.5</v>
+        <v>23.74</v>
       </c>
       <c r="H12" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" s="2">
         <v>1</v>
@@ -977,27 +961,27 @@
       <c r="O12" s="4"/>
       <c r="S12" s="4"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="G13" s="2">
+        <v>23.59</v>
       </c>
       <c r="H13" s="5">
         <v>0</v>
@@ -1012,62 +996,62 @@
       <c r="O13" s="4"/>
       <c r="S13" s="4"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G14" s="2">
-        <v>28</v>
+        <v>26.5</v>
       </c>
       <c r="H14" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" s="2">
         <v>1</v>
       </c>
       <c r="J14" s="2" cm="1">
         <f t="array" ref="J14">_xlfn.IFS(H14=0,0,H14=1,1,H14=2,1,H14=3,2,H14=4,2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" s="4"/>
       <c r="S14" s="4"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="2">
-        <v>31.16</v>
+        <v>10</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="H15" s="5">
         <v>0</v>
@@ -1082,62 +1066,62 @@
       <c r="O15" s="4"/>
       <c r="S15" s="4"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" s="2">
-        <v>20.100000000000001</v>
+        <v>28</v>
       </c>
       <c r="H16" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I16" s="2">
         <v>1</v>
       </c>
       <c r="J16" s="2" cm="1">
         <f t="array" ref="J16">_xlfn.IFS(H16=0,0,H16=1,1,H16=2,1,H16=3,2,H16=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" s="4"/>
       <c r="S16" s="4"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17" s="2">
-        <v>33.4</v>
+        <v>31.16</v>
       </c>
       <c r="H17" s="5">
         <v>0</v>
@@ -1152,135 +1136,135 @@
       <c r="O17" s="4"/>
       <c r="S17" s="4"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G18" s="2">
-        <v>35.299999999999997</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="H18" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="2" cm="1">
         <f t="array" ref="J18">_xlfn.IFS(H18=0,0,H18=1,1,H18=2,1,H18=3,2,H18=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O18" s="4"/>
       <c r="S18" s="4"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G19" s="2">
-        <v>25.8</v>
+        <v>33.4</v>
       </c>
       <c r="H19" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="2" cm="1">
         <f t="array" ref="J19">_xlfn.IFS(H19=0,0,H19=1,1,H19=2,1,H19=3,2,H19=4,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="4"/>
       <c r="S19" s="4"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G20" s="2">
-        <v>30.4</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="H20" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2" cm="1">
         <f t="array" ref="J20">_xlfn.IFS(H20=0,0,H20=1,1,H20=2,1,H20=3,2,H20=4,2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O20" s="4"/>
       <c r="S20" s="4"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G21" s="2">
-        <v>18.8</v>
+        <v>25.8</v>
       </c>
       <c r="H21" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="2">
         <v>1</v>
@@ -1292,59 +1276,62 @@
       <c r="O21" s="4"/>
       <c r="S21" s="4"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22" s="2">
-        <v>25.5</v>
+        <v>30.4</v>
       </c>
       <c r="H22" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I22" s="2">
         <v>1</v>
       </c>
       <c r="J22" s="2" cm="1">
         <f t="array" ref="J22">_xlfn.IFS(H22=0,0,H22=1,1,H22=2,1,H22=3,2,H22=4,2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O22" s="4"/>
       <c r="S22" s="4"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D23" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G23" s="2">
-        <v>24</v>
+        <v>18.8</v>
       </c>
       <c r="H23" s="5">
         <v>2</v>
@@ -1359,65 +1346,62 @@
       <c r="O23" s="4"/>
       <c r="S23" s="4"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G24" s="2">
-        <v>28.2</v>
+        <v>25.5</v>
       </c>
       <c r="H24" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24" s="2">
         <v>1</v>
       </c>
       <c r="J24" s="2" cm="1">
         <f t="array" ref="J24">_xlfn.IFS(H24=0,0,H24=1,1,H24=2,1,H24=3,2,H24=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" s="4"/>
       <c r="S24" s="4"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G25" s="2">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="H25" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="2">
         <v>1</v>
@@ -1429,62 +1413,62 @@
       <c r="O25" s="4"/>
       <c r="S25" s="4"/>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G26" s="2">
-        <v>30.2</v>
+        <v>28.2</v>
       </c>
       <c r="H26" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2" cm="1">
         <f t="array" ref="J26">_xlfn.IFS(H26=0,0,H26=1,1,H26=2,1,H26=3,2,H26=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O26" s="4"/>
       <c r="S26" s="4"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" s="2">
-        <v>28.8</v>
+        <v>24.5</v>
       </c>
       <c r="H27" s="5">
         <v>1</v>
@@ -1499,234 +1483,234 @@
       <c r="O27" s="4"/>
       <c r="S27" s="4"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G28" s="2">
-        <v>23.8</v>
+        <v>30.2</v>
       </c>
       <c r="H28" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="2" cm="1">
         <f t="array" ref="J28">_xlfn.IFS(H28=0,0,H28=1,1,H28=2,1,H28=3,2,H28=4,2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O28" s="4"/>
       <c r="S28" s="4"/>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G29" s="2">
-        <v>30.7</v>
+        <v>28.8</v>
       </c>
       <c r="H29" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I29" s="2">
         <v>1</v>
       </c>
       <c r="J29" s="2" cm="1">
         <f t="array" ref="J29">_xlfn.IFS(H29=0,0,H29=1,1,H29=2,1,H29=3,2,H29=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O29" s="4"/>
       <c r="S29" s="4"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D30" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G30" s="2">
-        <v>39</v>
+        <v>23.8</v>
       </c>
       <c r="H30" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I30" s="2">
         <v>1</v>
       </c>
       <c r="J30" s="2" cm="1">
         <f t="array" ref="J30">_xlfn.IFS(H30=0,0,H30=1,1,H30=2,1,H30=3,2,H30=4,2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" s="4"/>
       <c r="S30" s="4"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G31" s="2">
-        <v>36.5</v>
+        <v>30.7</v>
       </c>
       <c r="H31" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" s="2">
         <v>1</v>
       </c>
       <c r="J31" s="2" cm="1">
         <f t="array" ref="J31">_xlfn.IFS(H31=0,0,H31=1,1,H31=2,1,H31=3,2,H31=4,2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" s="4"/>
       <c r="S31" s="4"/>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G32" s="2">
-        <v>26.2</v>
+        <v>39</v>
       </c>
       <c r="H32" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I32" s="2">
         <v>1</v>
       </c>
       <c r="J32" s="2" cm="1">
         <f t="array" ref="J32">_xlfn.IFS(H32=0,0,H32=1,1,H32=2,1,H32=3,2,H32=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O32" s="4"/>
       <c r="S32" s="4"/>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G33" s="2">
-        <v>19.100000000000001</v>
+        <v>36.5</v>
       </c>
       <c r="H33" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I33" s="2">
         <v>1</v>
       </c>
       <c r="J33" s="2" cm="1">
         <f t="array" ref="J33">_xlfn.IFS(H33=0,0,H33=1,1,H33=2,1,H33=3,2,H33=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O33" s="4"/>
       <c r="S33" s="4"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G34" s="2">
-        <v>16.600000000000001</v>
+        <v>26.2</v>
       </c>
       <c r="H34" s="5">
         <v>4</v>
@@ -1741,62 +1725,62 @@
       <c r="O34" s="4"/>
       <c r="S34" s="4"/>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G35" s="2">
-        <v>21.7</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="H35" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" s="2">
         <v>1</v>
       </c>
       <c r="J35" s="2" cm="1">
         <f t="array" ref="J35">_xlfn.IFS(H35=0,0,H35=1,1,H35=2,1,H35=3,2,H35=4,2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O35" s="4"/>
       <c r="S35" s="4"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G36" s="2">
-        <v>29.6</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="H36" s="5">
         <v>4</v>
@@ -1811,62 +1795,65 @@
       <c r="O36" s="4"/>
       <c r="S36" s="4"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>317</v>
+        <v>315</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" s="2">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G37" s="2">
-        <v>24.9</v>
+        <v>21.7</v>
       </c>
       <c r="H37" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2" cm="1">
         <f t="array" ref="J37">_xlfn.IFS(H37=0,0,H37=1,1,H37=2,1,H37=3,2,H37=4,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" s="4"/>
       <c r="S37" s="4"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G38" s="2">
-        <v>13.5</v>
+        <v>29.6</v>
       </c>
       <c r="H38" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I38" s="2">
         <v>1</v>
@@ -1878,199 +1865,199 @@
       <c r="O38" s="4"/>
       <c r="S38" s="4"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>319</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>9</v>
+        <v>317</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G39" s="2">
-        <v>39.299999999999997</v>
+        <v>24.9</v>
       </c>
       <c r="H39" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="2" cm="1">
         <f t="array" ref="J39">_xlfn.IFS(H39=0,0,H39=1,1,H39=2,1,H39=3,2,H39=4,2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O39" s="4"/>
       <c r="S39" s="4"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G40" s="2">
-        <v>26.1</v>
+        <v>13.5</v>
       </c>
       <c r="H40" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I40" s="2">
         <v>1</v>
       </c>
       <c r="J40" s="2" cm="1">
         <f t="array" ref="J40">_xlfn.IFS(H40=0,0,H40=1,1,H40=2,1,H40=3,2,H40=4,2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40" s="4"/>
       <c r="S40" s="4"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41" s="2">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G41" s="2">
-        <v>24.6</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="H41" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="2" cm="1">
         <f t="array" ref="J41">_xlfn.IFS(H41=0,0,H41=1,1,H41=2,1,H41=3,2,H41=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O41" s="4"/>
       <c r="S41" s="4"/>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42" s="2">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G42" s="2">
-        <v>18.399999999999999</v>
+        <v>26.1</v>
       </c>
       <c r="H42" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I42" s="2">
         <v>1</v>
       </c>
       <c r="J42" s="2" cm="1">
         <f t="array" ref="J42">_xlfn.IFS(H42=0,0,H42=1,1,H42=2,1,H42=3,2,H42=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O42" s="4"/>
       <c r="S42" s="4"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D43" s="2">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G43" s="2">
-        <v>19.2</v>
+        <v>24.6</v>
       </c>
       <c r="H43" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" s="2" cm="1">
         <f t="array" ref="J43">_xlfn.IFS(H43=0,0,H43=1,1,H43=2,1,H43=3,2,H43=4,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" s="4"/>
       <c r="S43" s="4"/>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D44" s="2">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G44" s="2">
-        <v>19.2</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="H44" s="5">
         <v>4</v>
@@ -2085,27 +2072,27 @@
       <c r="O44" s="4"/>
       <c r="S44" s="4"/>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D45" s="2">
         <v>78</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G45" s="2">
-        <v>25.5</v>
+        <v>19.2</v>
       </c>
       <c r="H45" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" s="2">
         <v>1</v>
@@ -2117,237 +2104,234 @@
       <c r="O45" s="4"/>
       <c r="S45" s="4"/>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D46" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G46" s="2">
-        <v>25</v>
+        <v>19.2</v>
       </c>
       <c r="H46" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I46" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="2" cm="1">
         <f t="array" ref="J46">_xlfn.IFS(H46=0,0,H46=1,1,H46=2,1,H46=3,2,H46=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O46" s="4"/>
       <c r="S46" s="4"/>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D47" s="2">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G47" s="2">
-        <v>23.8</v>
+        <v>25.5</v>
       </c>
       <c r="H47" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I47" s="2">
         <v>1</v>
       </c>
       <c r="J47" s="2" cm="1">
         <f t="array" ref="J47">_xlfn.IFS(H47=0,0,H47=1,1,H47=2,1,H47=3,2,H47=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O47" s="4"/>
       <c r="S47" s="4"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D48" s="2">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G48" s="2">
-        <v>41.9</v>
+        <v>25</v>
       </c>
       <c r="H48" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="2" cm="1">
         <f t="array" ref="J48">_xlfn.IFS(H48=0,0,H48=1,1,H48=2,1,H48=3,2,H48=4,2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O48" s="4"/>
       <c r="S48" s="4"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D49" s="2">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G49" s="2">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="H49" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I49" s="2">
         <v>1</v>
       </c>
       <c r="J49" s="2" cm="1">
         <f t="array" ref="J49">_xlfn.IFS(H49=0,0,H49=1,1,H49=2,1,H49=3,2,H49=4,2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O49" s="4"/>
       <c r="S49" s="4"/>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D50" s="2">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G50" s="2">
-        <v>30.7</v>
+        <v>41.9</v>
       </c>
       <c r="H50" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I50" s="2">
         <v>1</v>
       </c>
       <c r="J50" s="2" cm="1">
         <f t="array" ref="J50">_xlfn.IFS(H50=0,0,H50=1,1,H50=2,1,H50=3,2,H50=4,2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O50" s="4"/>
       <c r="S50" s="4"/>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D51" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G51" s="2">
-        <v>35.4</v>
+        <v>26.9</v>
       </c>
       <c r="H51" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="2" cm="1">
         <f t="array" ref="J51">_xlfn.IFS(H51=0,0,H51=1,1,H51=2,1,H51=3,2,H51=4,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" s="4"/>
       <c r="S51" s="4"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D52" s="2">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G52" s="2">
-        <v>24.6</v>
+        <v>30.7</v>
       </c>
       <c r="H52" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" s="2">
         <v>1</v>
@@ -2359,161 +2343,164 @@
       <c r="O52" s="4"/>
       <c r="S52" s="4"/>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D53" s="2">
         <v>76</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G53" s="2">
-        <v>27.5</v>
+        <v>35.4</v>
       </c>
       <c r="H53" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" s="2" cm="1">
         <f t="array" ref="J53">_xlfn.IFS(H53=0,0,H53=1,1,H53=2,1,H53=3,2,H53=4,2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O53" s="4"/>
       <c r="S53" s="4"/>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D54" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G54" s="2">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="H54" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="2" cm="1">
         <f t="array" ref="J54">_xlfn.IFS(H54=0,0,H54=1,1,H54=2,1,H54=3,2,H54=4,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" s="4"/>
       <c r="S54" s="4"/>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D55" s="2">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G55" s="2">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="H55" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I55" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="2" cm="1">
         <f t="array" ref="J55">_xlfn.IFS(H55=0,0,H55=1,1,H55=2,1,H55=3,2,H55=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O55" s="4"/>
       <c r="S55" s="4"/>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>338</v>
+        <v>336</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D56" s="2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G56" s="2">
-        <v>25.5</v>
+        <v>24.3</v>
       </c>
       <c r="H56" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="2" cm="1">
         <f t="array" ref="J56">_xlfn.IFS(H56=0,0,H56=1,1,H56=2,1,H56=3,2,H56=4,2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O56" s="4"/>
       <c r="S56" s="4"/>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D57" s="2">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G57" s="2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H57" s="5">
         <v>0</v>
@@ -2528,62 +2515,59 @@
       <c r="O57" s="4"/>
       <c r="S57" s="4"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>340</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>9</v>
+        <v>338</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D58" s="2">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G58" s="2">
-        <v>27.9</v>
+        <v>25.5</v>
       </c>
       <c r="H58" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I58" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2" cm="1">
         <f t="array" ref="J58">_xlfn.IFS(H58=0,0,H58=1,1,H58=2,1,H58=3,2,H58=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O58" s="4"/>
       <c r="S58" s="4"/>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D59" s="2">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G59" s="2">
-        <v>44.6</v>
+        <v>32</v>
       </c>
       <c r="H59" s="5">
         <v>0</v>
@@ -2598,27 +2582,27 @@
       <c r="O59" s="4"/>
       <c r="S59" s="4"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D60" s="2">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G60" s="2">
-        <v>37.1</v>
+        <v>27.9</v>
       </c>
       <c r="H60" s="5">
         <v>0</v>
@@ -2633,27 +2617,27 @@
       <c r="O60" s="4"/>
       <c r="S60" s="4"/>
     </row>
-    <row r="61" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:19" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D61" s="2">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G61" s="2">
-        <v>28.7</v>
+        <v>44.6</v>
       </c>
       <c r="H61" s="5">
         <v>0</v>
@@ -2668,43 +2652,67 @@
       <c r="O61" s="4"/>
       <c r="S61" s="4"/>
     </row>
-    <row r="62" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="6">
-        <v>383</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>9</v>
+    <row r="62" spans="1:19" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="9">
+        <v>342</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2">
+        <v>37</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="2">
+        <v>37.1</v>
       </c>
       <c r="H62" s="5">
-        <v>1</v>
-      </c>
-      <c r="I62" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I62" s="2">
+        <v>0</v>
       </c>
       <c r="J62" s="2" cm="1">
         <f t="array" ref="J62">_xlfn.IFS(H62=0,0,H62=1,1,H62=2,1,H62=3,2,H62=4,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" s="4"/>
       <c r="S62" s="4"/>
     </row>
-    <row r="63" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="6">
-        <v>387</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>9</v>
+    <row r="63" spans="1:19" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="9">
+        <v>345</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2">
+        <v>34</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G63" s="2">
+        <v>28.7</v>
       </c>
       <c r="H63" s="5">
         <v>0</v>
       </c>
-      <c r="I63" s="5">
+      <c r="I63" s="2">
         <v>0</v>
       </c>
       <c r="J63" s="2" cm="1">
@@ -2714,38 +2722,50 @@
       <c r="O63" s="4"/>
       <c r="S63" s="4"/>
     </row>
-    <row r="64" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H64" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" s="2" cm="1">
         <f t="array" ref="J64">_xlfn.IFS(H64=0,0,H64=1,1,H64=2,1,H64=3,2,H64=4,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" s="4"/>
       <c r="S64" s="4"/>
     </row>
-    <row r="65" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H65" s="5">
         <v>0</v>
@@ -2760,15 +2780,21 @@
       <c r="O65" s="4"/>
       <c r="S65" s="4"/>
     </row>
-    <row r="66" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H66" s="5">
         <v>0</v>
@@ -2783,15 +2809,21 @@
       <c r="O66" s="4"/>
       <c r="S66" s="4"/>
     </row>
-    <row r="67" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H67" s="5">
         <v>0</v>
@@ -2806,64 +2838,82 @@
       <c r="O67" s="4"/>
       <c r="S67" s="4"/>
     </row>
-    <row r="68" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H68" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I68" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" s="2" cm="1">
         <f t="array" ref="J68">_xlfn.IFS(H68=0,0,H68=1,1,H68=2,1,H68=3,2,H68=4,2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O68" s="4"/>
       <c r="S68" s="4"/>
     </row>
-    <row r="69" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="H69" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="2" cm="1">
         <f t="array" ref="J69">_xlfn.IFS(H69=0,0,H69=1,1,H69=2,1,H69=3,2,H69=4,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" s="4"/>
       <c r="S69" s="4"/>
     </row>
-    <row r="70" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="H70" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I70" s="5">
         <v>1</v>
@@ -2875,38 +2925,50 @@
       <c r="O70" s="4"/>
       <c r="S70" s="4"/>
     </row>
-    <row r="71" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H71" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I71" s="5">
         <v>1</v>
       </c>
       <c r="J71" s="2" cm="1">
         <f t="array" ref="J71">_xlfn.IFS(H71=0,0,H71=1,1,H71=2,1,H71=3,2,H71=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O71" s="4"/>
       <c r="S71" s="4"/>
     </row>
-    <row r="72" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H72" s="5">
         <v>4</v>
@@ -2921,18 +2983,24 @@
       <c r="O72" s="4"/>
       <c r="S72" s="4"/>
     </row>
-    <row r="73" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H73" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I73" s="5">
         <v>1</v>
@@ -2944,43 +3012,51 @@
       <c r="O73" s="4"/>
       <c r="S73" s="4"/>
     </row>
-    <row r="74" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H74" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I74" s="5">
         <v>1</v>
       </c>
       <c r="J74" s="2" cm="1">
         <f t="array" ref="J74">_xlfn.IFS(H74=0,0,H74=1,1,H74=2,1,H74=3,2,H74=4,2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O74" s="4"/>
       <c r="S74" s="4"/>
     </row>
-    <row r="75" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="6">
-        <v>404</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H75" s="5">
-        <v>1</v>
-      </c>
-      <c r="I75" s="5">
+    <row r="75" spans="1:19" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="10">
+        <v>401</v>
+      </c>
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="E75" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H75" s="2">
+        <v>1</v>
+      </c>
+      <c r="I75" s="2">
         <v>1</v>
       </c>
       <c r="J75" s="2" cm="1">
@@ -2990,87 +3066,111 @@
       <c r="O75" s="4"/>
       <c r="S75" s="4"/>
     </row>
-    <row r="76" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H76" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I76" s="5">
         <v>1</v>
       </c>
       <c r="J76" s="2" cm="1">
         <f t="array" ref="J76">_xlfn.IFS(H76=0,0,H76=1,1,H76=2,1,H76=3,2,H76=4,2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O76" s="4"/>
       <c r="S76" s="4"/>
     </row>
-    <row r="77" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H77" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I77" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" s="2" cm="1">
         <f t="array" ref="J77">_xlfn.IFS(H77=0,0,H77=1,1,H77=2,1,H77=3,2,H77=4,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" s="4"/>
       <c r="S77" s="4"/>
     </row>
-    <row r="78" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H78" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I78" s="5">
         <v>1</v>
       </c>
       <c r="J78" s="2" cm="1">
         <f t="array" ref="J78">_xlfn.IFS(H78=0,0,H78=1,1,H78=2,1,H78=3,2,H78=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O78" s="4"/>
       <c r="S78" s="4"/>
     </row>
-    <row r="79" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H79" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79" s="5">
         <v>1</v>
@@ -3082,15 +3182,21 @@
       <c r="O79" s="4"/>
       <c r="S79" s="4"/>
     </row>
-    <row r="80" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H80" s="5">
         <v>0</v>
@@ -3105,37 +3211,55 @@
       <c r="O80" s="4"/>
       <c r="S80" s="4"/>
     </row>
-    <row r="81" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H81" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I81" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" s="2" cm="1">
         <f t="array" ref="J81">_xlfn.IFS(H81=0,0,H81=1,1,H81=2,1,H81=3,2,H81=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O81" s="4"/>
       <c r="S81" s="4"/>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A82" s="7">
-        <v>401</v>
-      </c>
-      <c r="H82" s="2">
-        <v>1</v>
-      </c>
-      <c r="I82" s="2">
+    <row r="82" spans="1:19" ht="20" x14ac:dyDescent="0.25">
+      <c r="A82" s="8">
+        <v>408</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H82" s="5">
+        <v>2</v>
+      </c>
+      <c r="I82" s="5">
         <v>1</v>
       </c>
       <c r="J82" s="2" cm="1">
@@ -3145,14 +3269,26 @@
       <c r="O82" s="4"/>
       <c r="S82" s="4"/>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A83" s="7">
-        <v>411</v>
-      </c>
-      <c r="H83" s="2">
-        <v>0</v>
-      </c>
-      <c r="I83" s="2">
+    <row r="83" spans="1:19" ht="20" x14ac:dyDescent="0.25">
+      <c r="A83" s="8">
+        <v>409</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H83" s="5">
+        <v>0</v>
+      </c>
+      <c r="I83" s="5">
         <v>0</v>
       </c>
       <c r="J83" s="2" cm="1">
@@ -3162,26 +3298,44 @@
       <c r="O83" s="4"/>
       <c r="S83" s="4"/>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A84" s="7">
-        <v>413</v>
-      </c>
-      <c r="H84" s="2">
-        <v>4</v>
-      </c>
-      <c r="I84" s="2">
-        <v>1</v>
+    <row r="84" spans="1:19" ht="20" x14ac:dyDescent="0.25">
+      <c r="A84" s="8">
+        <v>410</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H84" s="5">
+        <v>0</v>
+      </c>
+      <c r="I84" s="5">
+        <v>0</v>
       </c>
       <c r="J84" s="2" cm="1">
         <f t="array" ref="J84">_xlfn.IFS(H84=0,0,H84=1,1,H84=2,1,H84=3,2,H84=4,2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O84" s="4"/>
       <c r="S84" s="4"/>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="7">
-        <v>415</v>
+        <v>411</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H85" s="2">
         <v>0</v>
@@ -3196,9 +3350,15 @@
       <c r="O85" s="4"/>
       <c r="S85" s="4"/>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="7">
-        <v>416</v>
+        <v>413</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H86" s="2">
         <v>4</v>
@@ -3213,26 +3373,38 @@
       <c r="O86" s="4"/>
       <c r="S86" s="4"/>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="7">
-        <v>417</v>
+        <v>415</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H87" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" s="2" cm="1">
         <f t="array" ref="J87">_xlfn.IFS(H87=0,0,H87=1,1,H87=2,1,H87=3,2,H87=4,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" s="4"/>
       <c r="S87" s="4"/>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="7">
-        <v>418</v>
+        <v>416</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H88" s="2">
         <v>4</v>
@@ -3247,26 +3419,38 @@
       <c r="O88" s="4"/>
       <c r="S88" s="4"/>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="7">
-        <v>421</v>
+        <v>417</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" s="2" cm="1">
         <f t="array" ref="J89">_xlfn.IFS(H89=0,0,H89=1,1,H89=2,1,H89=3,2,H89=4,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" s="4"/>
       <c r="S89" s="4"/>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="7">
-        <v>424</v>
+        <v>418</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H90" s="2">
         <v>4</v>
@@ -3281,27 +3465,39 @@
       <c r="O90" s="4"/>
       <c r="S90" s="4"/>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="7">
-        <v>420</v>
+        <v>418</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H91" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I91" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" s="2" cm="1">
         <f t="array" ref="J91">_xlfn.IFS(H91=0,0,H91=1,1,H91=2,1,H91=3,2,H91=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O91" s="4"/>
       <c r="S91" s="4"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="7">
         <v>419</v>
       </c>
+      <c r="E92" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="H92" s="2">
         <v>1</v>
       </c>
@@ -3315,43 +3511,61 @@
       <c r="O92" s="4"/>
       <c r="S92" s="4"/>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="7">
-        <v>425</v>
+        <v>420</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H93" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" s="2" cm="1">
         <f t="array" ref="J93">_xlfn.IFS(H93=0,0,H93=1,1,H93=2,1,H93=3,2,H93=4,2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O93" s="4"/>
       <c r="S93" s="4"/>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="7">
-        <v>426</v>
+        <v>421</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H94" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I94" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" s="2" cm="1">
         <f t="array" ref="J94">_xlfn.IFS(H94=0,0,H94=1,1,H94=2,1,H94=3,2,H94=4,2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O94" s="4"/>
       <c r="S94" s="4"/>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="7">
-        <v>427</v>
+        <v>424</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H95" s="2">
         <v>4</v>
@@ -3366,43 +3580,61 @@
       <c r="O95" s="4"/>
       <c r="S95" s="4"/>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="7">
-        <v>428</v>
+        <v>425</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H96" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I96" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" s="2" cm="1">
         <f t="array" ref="J96">_xlfn.IFS(H96=0,0,H96=1,1,H96=2,1,H96=3,2,H96=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O96" s="4"/>
       <c r="S96" s="4"/>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" s="7">
-        <v>432</v>
+        <v>426</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H97" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I97" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" s="2" cm="1">
         <f t="array" ref="J97">_xlfn.IFS(H97=0,0,H97=1,1,H97=2,1,H97=3,2,H97=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O97" s="4"/>
       <c r="S97" s="4"/>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" s="7">
-        <v>429</v>
+        <v>427</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H98" s="2">
         <v>4</v>
@@ -3417,60 +3649,84 @@
       <c r="O98" s="4"/>
       <c r="S98" s="4"/>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="7">
-        <v>430</v>
+        <v>428</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H99" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" s="2" cm="1">
         <f t="array" ref="J99">_xlfn.IFS(H99=0,0,H99=1,1,H99=2,1,H99=3,2,H99=4,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O99" s="4"/>
       <c r="S99" s="4"/>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" s="7">
-        <v>433</v>
+        <v>429</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H100" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I100" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" s="2" cm="1">
         <f t="array" ref="J100">_xlfn.IFS(H100=0,0,H100=1,1,H100=2,1,H100=3,2,H100=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O100" s="4"/>
       <c r="S100" s="4"/>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" s="7">
-        <v>431</v>
+        <v>430</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H101" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I101" s="2">
         <v>1</v>
       </c>
       <c r="J101" s="2" cm="1">
         <f t="array" ref="J101">_xlfn.IFS(H101=0,0,H101=1,1,H101=2,1,H101=3,2,H101=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O101" s="4"/>
       <c r="S101" s="4"/>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="7">
-        <v>435</v>
+        <v>431</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H102" s="2">
         <v>4</v>
@@ -3485,44 +3741,62 @@
       <c r="O102" s="4"/>
       <c r="S102" s="4"/>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" s="7">
-        <v>438</v>
+        <v>432</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H103" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I103" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" s="2" cm="1">
         <f t="array" ref="J103">_xlfn.IFS(H103=0,0,H103=1,1,H103=2,1,H103=3,2,H103=4,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O103" s="4"/>
       <c r="S103" s="4"/>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" s="7">
-        <v>191</v>
+        <v>433</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H104" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I104" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" s="2" cm="1">
         <f t="array" ref="J104">_xlfn.IFS(H104=0,0,H104=1,1,H104=2,1,H104=3,2,H104=4,2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O104" s="4"/>
       <c r="S104" s="4"/>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" s="7">
         <v>434</v>
       </c>
+      <c r="E105" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H105" s="2">
         <v>1</v>
       </c>
@@ -3536,9 +3810,15 @@
       <c r="O105" s="4"/>
       <c r="S105" s="4"/>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" s="7">
-        <v>440</v>
+        <v>435</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H106" s="2">
         <v>4</v>
@@ -3553,12 +3833,18 @@
       <c r="O106" s="4"/>
       <c r="S106" s="4"/>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" s="7">
-        <v>439</v>
+        <v>436</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H107" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I107" s="2">
         <v>1</v>
@@ -3570,10 +3856,16 @@
       <c r="O107" s="4"/>
       <c r="S107" s="4"/>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" s="7">
         <v>437</v>
       </c>
+      <c r="E108" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H108" s="2">
         <v>2</v>
       </c>
@@ -3587,29 +3879,41 @@
       <c r="O108" s="4"/>
       <c r="S108" s="4"/>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" s="7">
-        <v>441</v>
+        <v>438</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H109" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I109" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" s="2" cm="1">
         <f t="array" ref="J109">_xlfn.IFS(H109=0,0,H109=1,1,H109=2,1,H109=3,2,H109=4,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O109" s="4"/>
       <c r="S109" s="4"/>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" s="7">
-        <v>436</v>
+        <v>439</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H110" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I110" s="2">
         <v>1</v>
@@ -3621,26 +3925,38 @@
       <c r="O110" s="4"/>
       <c r="S110" s="4"/>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" s="7">
-        <v>445</v>
+        <v>439</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H111" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I111" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" s="2" cm="1">
         <f t="array" ref="J111">_xlfn.IFS(H111=0,0,H111=1,1,H111=2,1,H111=3,2,H111=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O111" s="4"/>
       <c r="S111" s="4"/>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="7">
-        <v>444</v>
+        <v>440</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H112" s="2">
         <v>4</v>
@@ -3655,46 +3971,64 @@
       <c r="O112" s="4"/>
       <c r="S112" s="4"/>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" s="7">
-        <v>442</v>
+        <v>441</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H113" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J113" s="2" cm="1">
         <f t="array" ref="J113">_xlfn.IFS(H113=0,0,H113=1,1,H113=2,1,H113=3,2,H113=4,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O113" s="4"/>
       <c r="S113" s="4"/>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" s="7">
-        <v>443</v>
+        <v>442</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H114" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I114" s="2">
         <v>1</v>
       </c>
       <c r="J114" s="2" cm="1">
         <f t="array" ref="J114">_xlfn.IFS(H114=0,0,H114=1,1,H114=2,1,H114=3,2,H114=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O114" s="4"/>
       <c r="S114" s="4"/>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" s="7">
-        <v>448</v>
+        <v>443</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H115" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I115" s="2">
         <v>1</v>
@@ -3706,9 +4040,15 @@
       <c r="O115" s="4"/>
       <c r="S115" s="4"/>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" s="7">
-        <v>446</v>
+        <v>444</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H116" s="2">
         <v>4</v>
@@ -3723,111 +4063,153 @@
       <c r="O116" s="4"/>
       <c r="S116" s="4"/>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" s="7">
-        <v>450</v>
+        <v>445</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H117" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117" s="2" cm="1">
         <f t="array" ref="J117">_xlfn.IFS(H117=0,0,H117=1,1,H117=2,1,H117=3,2,H117=4,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O117" s="4"/>
       <c r="S117" s="4"/>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" s="7">
-        <v>449</v>
+        <v>446</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="H118" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I118" s="2">
         <v>1</v>
       </c>
       <c r="J118" s="2" cm="1">
         <f t="array" ref="J118">_xlfn.IFS(H118=0,0,H118=1,1,H118=2,1,H118=3,2,H118=4,2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O118" s="4"/>
       <c r="S118" s="4"/>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" s="7">
-        <v>451</v>
+        <v>448</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H119" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I119" s="2">
         <v>1</v>
       </c>
       <c r="J119" s="2" cm="1">
         <f t="array" ref="J119">_xlfn.IFS(H119=0,0,H119=1,1,H119=2,1,H119=3,2,H119=4,2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O119" s="4"/>
       <c r="S119" s="4"/>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" s="7">
-        <v>452</v>
+        <v>449</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H120" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I120" s="2">
         <v>1</v>
       </c>
       <c r="J120" s="2" cm="1">
         <f t="array" ref="J120">_xlfn.IFS(H120=0,0,H120=1,1,H120=2,1,H120=3,2,H120=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O120" s="4"/>
       <c r="S120" s="4"/>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" s="7">
-        <v>454</v>
+        <v>450</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H121" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I121" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" s="2" cm="1">
         <f t="array" ref="J121">_xlfn.IFS(H121=0,0,H121=1,1,H121=2,1,H121=3,2,H121=4,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O121" s="4"/>
       <c r="S121" s="4"/>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" s="7">
-        <v>456</v>
+        <v>451</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H122" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I122" s="2">
         <v>1</v>
       </c>
       <c r="J122" s="2" cm="1">
         <f t="array" ref="J122">_xlfn.IFS(H122=0,0,H122=1,1,H122=2,1,H122=3,2,H122=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O122" s="4"/>
       <c r="S122" s="4"/>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" s="7">
-        <v>455</v>
+        <v>452</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H123" s="2">
         <v>4</v>
@@ -3842,111 +4224,153 @@
       <c r="O123" s="4"/>
       <c r="S123" s="4"/>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" s="7">
-        <v>458</v>
+        <v>454</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H124" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I124" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" s="2" cm="1">
         <f t="array" ref="J124">_xlfn.IFS(H124=0,0,H124=1,1,H124=2,1,H124=3,2,H124=4,2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O124" s="4"/>
       <c r="S124" s="4"/>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" s="7">
-        <v>459</v>
+        <v>455</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H125" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I125" s="2">
         <v>1</v>
       </c>
       <c r="J125" s="2" cm="1">
         <f t="array" ref="J125">_xlfn.IFS(H125=0,0,H125=1,1,H125=2,1,H125=3,2,H125=4,2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O125" s="4"/>
       <c r="S125" s="4"/>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" s="7">
-        <v>465</v>
+        <v>456</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H126" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I126" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" s="2" cm="1">
         <f t="array" ref="J126">_xlfn.IFS(H126=0,0,H126=1,1,H126=2,1,H126=3,2,H126=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O126" s="4"/>
       <c r="S126" s="4"/>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" s="7">
-        <v>468</v>
+        <v>458</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H127" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I127" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127" s="2" cm="1">
         <f t="array" ref="J127">_xlfn.IFS(H127=0,0,H127=1,1,H127=2,1,H127=3,2,H127=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O127" s="4"/>
       <c r="S127" s="4"/>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" s="7">
-        <v>462</v>
+        <v>459</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H128" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I128" s="2">
         <v>1</v>
       </c>
       <c r="J128" s="2" cm="1">
         <f t="array" ref="J128">_xlfn.IFS(H128=0,0,H128=1,1,H128=2,1,H128=3,2,H128=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O128" s="4"/>
       <c r="S128" s="4"/>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A129" s="7">
-        <v>471</v>
+        <v>462</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H129" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I129" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129" s="2" cm="1">
         <f t="array" ref="J129">_xlfn.IFS(H129=0,0,H129=1,1,H129=2,1,H129=3,2,H129=4,2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O129" s="4"/>
       <c r="S129" s="4"/>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130" s="7">
-        <v>473</v>
+        <v>465</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H130" s="2">
         <v>0</v>
@@ -3961,26 +4385,38 @@
       <c r="O130" s="4"/>
       <c r="S130" s="4"/>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" s="7">
-        <v>474</v>
+        <v>468</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H131" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I131" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131" s="2" cm="1">
         <f t="array" ref="J131">_xlfn.IFS(H131=0,0,H131=1,1,H131=2,1,H131=3,2,H131=4,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O131" s="4"/>
       <c r="S131" s="4"/>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132" s="7">
-        <v>472</v>
+        <v>471</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H132" s="2">
         <v>0</v>
@@ -3995,26 +4431,38 @@
       <c r="O132" s="4"/>
       <c r="S132" s="4"/>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A133" s="7">
-        <v>478</v>
+        <v>472</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="H133" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J133" s="2" cm="1">
         <f t="array" ref="J133">_xlfn.IFS(H133=0,0,H133=1,1,H133=2,1,H133=3,2,H133=4,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O133" s="4"/>
       <c r="S133" s="4"/>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134" s="7">
-        <v>479</v>
+        <v>473</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H134" s="2">
         <v>0</v>
@@ -4029,94 +4477,130 @@
       <c r="O134" s="4"/>
       <c r="S134" s="4"/>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135" s="7">
-        <v>482</v>
+        <v>474</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H135" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I135" s="2">
         <v>1</v>
       </c>
       <c r="J135" s="2" cm="1">
         <f t="array" ref="J135">_xlfn.IFS(H135=0,0,H135=1,1,H135=2,1,H135=3,2,H135=4,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O135" s="4"/>
       <c r="S135" s="4"/>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A136" s="7">
-        <v>485</v>
+        <v>477</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H136" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I136" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J136" s="2" cm="1">
         <f t="array" ref="J136">_xlfn.IFS(H136=0,0,H136=1,1,H136=2,1,H136=3,2,H136=4,2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O136" s="4"/>
       <c r="S136" s="4"/>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A137" s="7">
-        <v>491</v>
+        <v>478</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J137" s="2" cm="1">
         <f t="array" ref="J137">_xlfn.IFS(H137=0,0,H137=1,1,H137=2,1,H137=3,2,H137=4,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O137" s="4"/>
       <c r="S137" s="4"/>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" s="7">
-        <v>483</v>
+        <v>479</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H138" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I138" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J138" s="2" cm="1">
         <f t="array" ref="J138">_xlfn.IFS(H138=0,0,H138=1,1,H138=2,1,H138=3,2,H138=4,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O138" s="4"/>
       <c r="S138" s="4"/>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139" s="7">
-        <v>484</v>
+        <v>482</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H139" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I139" s="2">
         <v>1</v>
       </c>
       <c r="J139" s="2" cm="1">
         <f t="array" ref="J139">_xlfn.IFS(H139=0,0,H139=1,1,H139=2,1,H139=3,2,H139=4,2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O139" s="4"/>
       <c r="S139" s="4"/>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140" s="7">
-        <v>487</v>
+        <v>483</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H140" s="2">
         <v>1</v>
@@ -4131,56 +4615,80 @@
       <c r="O140" s="4"/>
       <c r="S140" s="4"/>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" s="7">
-        <v>477</v>
+        <v>484</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H141" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J141" s="2" cm="1">
         <f t="array" ref="J141">_xlfn.IFS(H141=0,0,H141=1,1,H141=2,1,H141=3,2,H141=4,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O141" s="4"/>
       <c r="S141" s="4"/>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" s="7">
-        <v>489</v>
+        <v>485</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H142" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J142" s="2" cm="1">
         <f t="array" ref="J142">_xlfn.IFS(H142=0,0,H142=1,1,H142=2,1,H142=3,2,H142=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" s="7">
-        <v>488</v>
+        <v>487</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H143" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I143" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143" s="2" cm="1">
         <f t="array" ref="J143">_xlfn.IFS(H143=0,0,H143=1,1,H143=2,1,H143=3,2,H143=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" s="7">
-        <v>493</v>
+        <v>488</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H144" s="2">
         <v>0</v>
@@ -4193,39 +4701,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="7">
-        <v>490</v>
+        <v>489</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H145" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" s="2" cm="1">
         <f t="array" ref="J145">_xlfn.IFS(H145=0,0,H145=1,1,H145=2,1,H145=3,2,H145=4,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="7">
-        <v>494</v>
+        <v>490</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H146" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I146" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" s="2" cm="1">
         <f t="array" ref="J146">_xlfn.IFS(H146=0,0,H146=1,1,H146=2,1,H146=3,2,H146=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="7">
-        <v>498</v>
+        <v>491</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H147" s="2">
         <v>0</v>
@@ -4238,24 +4764,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="7">
-        <v>499</v>
+        <v>493</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H148" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I148" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148" s="2" cm="1">
         <f t="array" ref="J148">_xlfn.IFS(H148=0,0,H148=1,1,H148=2,1,H148=3,2,H148=4,2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="7">
-        <v>501</v>
+        <v>494</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H149" s="2">
         <v>0</v>
@@ -4268,9 +4806,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="7">
-        <v>502</v>
+        <v>498</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H150" s="2">
         <v>0</v>
@@ -4283,12 +4827,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="7">
-        <v>500</v>
+        <v>499</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H151" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I151" s="2">
         <v>1</v>
@@ -4298,100 +4848,142 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="7">
-        <v>505</v>
+        <v>500</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H152" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I152" s="2">
         <v>1</v>
       </c>
       <c r="J152" s="2" cm="1">
         <f t="array" ref="J152">_xlfn.IFS(H152=0,0,H152=1,1,H152=2,1,H152=3,2,H152=4,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="7">
-        <v>418</v>
+        <v>501</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H153" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I153" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" s="2" cm="1">
         <f t="array" ref="J153">_xlfn.IFS(H153=0,0,H153=1,1,H153=2,1,H153=3,2,H153=4,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="7">
-        <v>506</v>
+        <v>502</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="H154" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I154" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J154" s="2" cm="1">
         <f t="array" ref="J154">_xlfn.IFS(H154=0,0,H154=1,1,H154=2,1,H154=3,2,H154=4,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="7">
-        <v>508</v>
+        <v>505</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H155" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I155" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J155" s="2" cm="1">
         <f t="array" ref="J155">_xlfn.IFS(H155=0,0,H155=1,1,H155=2,1,H155=3,2,H155=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="7">
-        <v>510</v>
+        <v>506</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H156" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I156" s="2">
         <v>1</v>
       </c>
       <c r="J156" s="2" cm="1">
         <f t="array" ref="J156">_xlfn.IFS(H156=0,0,H156=1,1,H156=2,1,H156=3,2,H156=4,2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="7">
-        <v>515</v>
+        <v>508</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H157" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I157" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J157" s="2" cm="1">
         <f t="array" ref="J157">_xlfn.IFS(H157=0,0,H157=1,1,H157=2,1,H157=3,2,H157=4,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="7">
         <v>509</v>
       </c>
+      <c r="E158" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H158" s="2">
         <v>2</v>
       </c>
@@ -4403,55 +4995,79 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="7">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H159" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I159" s="2">
         <v>1</v>
       </c>
       <c r="J159" s="2" cm="1">
         <f t="array" ref="J159">_xlfn.IFS(H159=0,0,H159=1,1,H159=2,1,H159=3,2,H159=4,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="7">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H160" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I160" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160" s="2" cm="1">
         <f t="array" ref="J160">_xlfn.IFS(H160=0,0,H160=1,1,H160=2,1,H160=3,2,H160=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="7">
-        <v>518</v>
+        <v>512</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H161" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I161" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J161" s="2" cm="1">
         <f t="array" ref="J161">_xlfn.IFS(H161=0,0,H161=1,1,H161=2,1,H161=3,2,H161=4,2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="7">
         <v>514</v>
       </c>
+      <c r="E162" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H162" s="2">
         <v>4</v>
       </c>
@@ -4463,42 +5079,60 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="7">
-        <v>516</v>
+        <v>515</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H163" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I163" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" s="2" cm="1">
         <f t="array" ref="J163">_xlfn.IFS(H163=0,0,H163=1,1,H163=2,1,H163=3,2,H163=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="7">
-        <v>517</v>
+        <v>516</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H164" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I164" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J164" s="2" cm="1">
         <f t="array" ref="J164">_xlfn.IFS(H164=0,0,H164=1,1,H164=2,1,H164=3,2,H164=4,2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="7">
-        <v>519</v>
+        <v>517</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H165" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I165" s="2">
         <v>1</v>
@@ -4508,39 +5142,57 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="7">
-        <v>520</v>
+        <v>518</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H166" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I166" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J166" s="2" cm="1">
         <f t="array" ref="J166">_xlfn.IFS(H166=0,0,H166=1,1,H166=2,1,H166=3,2,H166=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="7">
-        <v>526</v>
+        <v>519</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="H167" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I167" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J167" s="2" cm="1">
         <f t="array" ref="J167">_xlfn.IFS(H167=0,0,H167=1,1,H167=2,1,H167=3,2,H167=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="7">
-        <v>522</v>
+        <v>520</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H168" s="2">
         <v>0</v>
@@ -4553,69 +5205,99 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="7">
-        <v>523</v>
+        <v>521</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H169" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I169" s="2">
         <v>1</v>
       </c>
       <c r="J169" s="2" cm="1">
         <f t="array" ref="J169">_xlfn.IFS(H169=0,0,H169=1,1,H169=2,1,H169=3,2,H169=4,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="7">
-        <v>524</v>
+        <v>522</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H170" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I170" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J170" s="2" cm="1">
         <f t="array" ref="J170">_xlfn.IFS(H170=0,0,H170=1,1,H170=2,1,H170=3,2,H170=4,2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="7">
-        <v>166</v>
+        <v>523</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H171" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I171" s="2">
         <v>1</v>
       </c>
       <c r="J171" s="2" cm="1">
         <f t="array" ref="J171">_xlfn.IFS(H171=0,0,H171=1,1,H171=2,1,H171=3,2,H171=4,2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="7">
-        <v>528</v>
+        <v>524</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H172" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J172" s="2" cm="1">
         <f t="array" ref="J172">_xlfn.IFS(H172=0,0,H172=1,1,H172=2,1,H172=3,2,H172=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="7">
-        <v>529</v>
+        <v>526</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H173" s="2">
         <v>0</v>
@@ -4628,70 +5310,100 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="7">
-        <v>530</v>
+        <v>528</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="H174" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I174" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J174" s="2" cm="1">
         <f t="array" ref="J174">_xlfn.IFS(H174=0,0,H174=1,1,H174=2,1,H174=3,2,H174=4,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="7">
-        <v>531</v>
+        <v>529</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H175" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I175" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J175" s="2" cm="1">
         <f t="array" ref="J175">_xlfn.IFS(H175=0,0,H175=1,1,H175=2,1,H175=3,2,H175=4,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="7">
-        <v>521</v>
+        <v>530</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H176" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I176" s="2">
         <v>1</v>
       </c>
       <c r="J176" s="2" cm="1">
         <f t="array" ref="J176">_xlfn.IFS(H176=0,0,H176=1,1,H176=2,1,H176=3,2,H176=4,2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="7">
-        <v>536</v>
+        <v>531</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H177" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I177" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J177" s="2" cm="1">
         <f t="array" ref="J177">_xlfn.IFS(H177=0,0,H177=1,1,H177=2,1,H177=3,2,H177=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="7">
         <v>533</v>
       </c>
+      <c r="E178" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H178" s="2">
         <v>4</v>
       </c>
@@ -4703,10 +5415,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" s="7">
         <v>534</v>
       </c>
+      <c r="E179" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H179" s="2">
         <v>0</v>
       </c>
@@ -4718,27 +5436,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" s="7">
-        <v>537</v>
+        <v>536</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H180" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I180" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J180" s="2" cm="1">
         <f t="array" ref="J180">_xlfn.IFS(H180=0,0,H180=1,1,H180=2,1,H180=3,2,H180=4,2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="7">
-        <v>538</v>
+        <v>537</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H181" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I181" s="2">
         <v>1</v>
@@ -4748,39 +5478,57 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="7">
-        <v>539</v>
+        <v>538</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="H182" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I182" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J182" s="2" cm="1">
         <f t="array" ref="J182">_xlfn.IFS(H182=0,0,H182=1,1,H182=2,1,H182=3,2,H182=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" s="7">
-        <v>540</v>
+        <v>539</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="H183" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I183" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J183" s="2" cm="1">
         <f t="array" ref="J183">_xlfn.IFS(H183=0,0,H183=1,1,H183=2,1,H183=3,2,H183=4,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="7">
-        <v>544</v>
+        <v>540</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H184" s="2">
         <v>4</v>
@@ -4793,24 +5541,36 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="7">
-        <v>545</v>
+        <v>544</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H185" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I185" s="2">
         <v>1</v>
       </c>
       <c r="J185" s="2" cm="1">
         <f t="array" ref="J185">_xlfn.IFS(H185=0,0,H185=1,1,H185=2,1,H185=3,2,H185=4,2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" s="7">
-        <v>546</v>
+        <v>545</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H186" s="2">
         <v>1</v>
@@ -4823,85 +5583,121 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="7">
-        <v>550</v>
+        <v>546</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H187" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I187" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J187" s="2" cm="1">
         <f t="array" ref="J187">_xlfn.IFS(H187=0,0,H187=1,1,H187=2,1,H187=3,2,H187=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="7">
-        <v>551</v>
+        <v>548</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="H188" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I188" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J188" s="2" cm="1">
         <f t="array" ref="J188">_xlfn.IFS(H188=0,0,H188=1,1,H188=2,1,H188=3,2,H188=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="7">
-        <v>548</v>
+        <v>549</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H189" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I189" s="2">
         <v>1</v>
       </c>
       <c r="J189" s="2" cm="1">
         <f t="array" ref="J189">_xlfn.IFS(H189=0,0,H189=1,1,H189=2,1,H189=3,2,H189=4,2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="7">
-        <v>549</v>
+        <v>550</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H190" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I190" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J190" s="2" cm="1">
         <f t="array" ref="J190">_xlfn.IFS(H190=0,0,H190=1,1,H190=2,1,H190=3,2,H190=4,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="7">
-        <v>553</v>
+        <v>551</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H191" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I191" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J191" s="2" cm="1">
         <f t="array" ref="J191">_xlfn.IFS(H191=0,0,H191=1,1,H191=2,1,H191=3,2,H191=4,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="7">
         <v>552</v>
       </c>
+      <c r="E192" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H192" s="2">
         <v>4</v>
       </c>
@@ -4913,25 +5709,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="7">
-        <v>555</v>
+        <v>553</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H193" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I193" s="2">
         <v>1</v>
       </c>
       <c r="J193" s="2" cm="1">
         <f t="array" ref="J193">_xlfn.IFS(H193=0,0,H193=1,1,H193=2,1,H193=3,2,H193=4,2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" s="7">
         <v>554</v>
       </c>
+      <c r="E194" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H194" s="2">
         <v>2</v>
       </c>
@@ -4943,40 +5751,58 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="7">
-        <v>560</v>
+        <v>555</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H195" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I195" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J195" s="2" cm="1">
         <f t="array" ref="J195">_xlfn.IFS(H195=0,0,H195=1,1,H195=2,1,H195=3,2,H195=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" s="7">
-        <v>439</v>
+        <v>560</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H196" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I196" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J196" s="2" cm="1">
         <f t="array" ref="J196">_xlfn.IFS(H196=0,0,H196=1,1,H196=2,1,H196=3,2,H196=4,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="7">
         <v>563</v>
       </c>
+      <c r="E197" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H197" s="2">
         <v>1</v>
       </c>
@@ -4988,10 +5814,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="7">
         <v>564</v>
       </c>
+      <c r="E198" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H198" s="2">
         <v>1</v>
       </c>
@@ -5003,12 +5835,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="7">
-        <v>568</v>
+        <v>565</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H199" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I199" s="2">
         <v>1</v>
@@ -5018,10 +5856,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="7">
         <v>566</v>
       </c>
+      <c r="E200" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H200" s="2">
         <v>4</v>
       </c>
@@ -5033,10 +5877,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="7">
         <v>567</v>
       </c>
+      <c r="E201" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H201" s="2">
         <v>3</v>
       </c>
@@ -5048,25 +5898,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="7">
-        <v>570</v>
+        <v>568</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H202" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I202" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J202" s="2" cm="1">
         <f t="array" ref="J202">_xlfn.IFS(H202=0,0,H202=1,1,H202=2,1,H202=3,2,H202=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="7">
         <v>569</v>
       </c>
+      <c r="E203" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="H203" s="2">
         <v>4</v>
       </c>
@@ -5078,9 +5940,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="7">
-        <v>572</v>
+        <v>570</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H204" s="2">
         <v>0</v>
@@ -5093,9 +5961,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="7">
-        <v>573</v>
+        <v>572</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H205" s="2">
         <v>0</v>
@@ -5108,24 +5982,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="7">
-        <v>565</v>
+        <v>573</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H206" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I206" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J206" s="2" cm="1">
         <f t="array" ref="J206">_xlfn.IFS(H206=0,0,H206=1,1,H206=2,1,H206=3,2,H206=4,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="7">
-        <v>576</v>
+        <v>575</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H207" s="2">
         <v>4</v>
@@ -5138,9 +6024,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="7">
-        <v>578</v>
+        <v>576</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H208" s="2">
         <v>4</v>
@@ -5153,12 +6045,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="7">
-        <v>579</v>
+        <v>577</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H209" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I209" s="2">
         <v>1</v>
@@ -5168,9 +6066,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="7">
-        <v>575</v>
+        <v>578</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H210" s="2">
         <v>4</v>
@@ -5183,12 +6087,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="7">
-        <v>577</v>
+        <v>579</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H211" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I211" s="2">
         <v>1</v>
@@ -5198,10 +6108,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="7">
         <v>580</v>
       </c>
+      <c r="E212" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H212" s="2">
         <v>4</v>
       </c>
@@ -5213,10 +6129,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="7">
         <v>581</v>
       </c>
+      <c r="E213" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H213" s="2">
         <v>0</v>
       </c>
@@ -5228,10 +6150,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="7">
         <v>583</v>
       </c>
+      <c r="E214" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H214" s="2">
         <v>4</v>
       </c>
@@ -5243,10 +6171,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="7">
         <v>585</v>
       </c>
+      <c r="E215" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="H215" s="2">
         <v>3</v>
       </c>
@@ -5258,24 +6192,36 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="7">
-        <v>590</v>
+        <v>586</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H216" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I216" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J216" s="2" cm="1">
         <f t="array" ref="J216">_xlfn.IFS(H216=0,0,H216=1,1,H216=2,1,H216=3,2,H216=4,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="7">
-        <v>591</v>
+        <v>589</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H217" s="2">
         <v>0</v>
@@ -5288,24 +6234,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="7">
-        <v>586</v>
+        <v>590</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H218" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I218" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J218" s="2" cm="1">
         <f t="array" ref="J218">_xlfn.IFS(H218=0,0,H218=1,1,H218=2,1,H218=3,2,H218=4,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="7">
-        <v>589</v>
+        <v>591</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="H219" s="2">
         <v>0</v>
@@ -5319,6 +6277,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K219">
+    <sortCondition ref="A153:A219"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/noodlepy/data/Biofluid_list_annotated_v4.xlsx
+++ b/noodlepy/data/Biofluid_list_annotated_v4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yifeigu/Documents/Carney_Lab/NoodlePy/noodlepy/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED8611D-07BC-D248-BCB5-4BE474D4C10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB4CA3F-329E-6A4B-B3D8-B3C99C2F63AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34080" yWindow="500" windowWidth="30240" windowHeight="18880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -212,15 +212,31 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,21 +554,23 @@
   <dimension ref="A1:S219"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" style="10" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="2" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="2" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="0" style="2" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="11" style="2"/>
-    <col min="6" max="6" width="27.83203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11" style="10"/>
+    <col min="6" max="6" width="27.83203125" style="15" customWidth="1"/>
     <col min="7" max="7" width="11" style="2"/>
     <col min="8" max="8" width="18.5" style="2" customWidth="1"/>
-    <col min="9" max="14" width="11" style="2"/>
+    <col min="9" max="9" width="11" style="2"/>
+    <col min="10" max="11" width="0" style="2" hidden="1" customWidth="1"/>
+    <col min="12" max="14" width="11" style="2"/>
     <col min="15" max="15" width="11" style="3"/>
     <col min="16" max="16384" width="11" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -564,10 +582,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="14" t="s">
         <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -576,18 +594,18 @@
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="10">
         <v>166</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="2">
@@ -604,13 +622,13 @@
       <c r="S2" s="4"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="10">
         <v>191</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H3" s="2">
@@ -627,7 +645,7 @@
       <c r="S3" s="4"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="A4" s="10">
         <v>272</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -639,10 +657,10 @@
       <c r="D4" s="2">
         <v>73</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G4" s="2">
@@ -666,7 +684,7 @@
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="A5" s="10">
         <v>275</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -678,10 +696,10 @@
       <c r="D5" s="2">
         <v>86</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="2">
@@ -705,7 +723,7 @@
       <c r="S5" s="4"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6" s="10">
         <v>276</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -717,10 +735,10 @@
       <c r="D6" s="2">
         <v>63</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="2">
@@ -744,7 +762,7 @@
       <c r="S6" s="4"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7" s="10">
         <v>277</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -756,10 +774,10 @@
       <c r="D7" s="2">
         <v>30</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="2">
@@ -783,7 +801,7 @@
       <c r="S7" s="4"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="A8" s="10">
         <v>278</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -795,10 +813,10 @@
       <c r="D8" s="2">
         <v>27</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="E8" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="2">
@@ -822,7 +840,7 @@
       <c r="S8" s="4"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9" s="10">
         <v>279</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -834,10 +852,10 @@
       <c r="D9" s="2">
         <v>29</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="E9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G9" s="2">
@@ -857,7 +875,7 @@
       <c r="S9" s="4"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="10">
         <v>280</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -869,10 +887,10 @@
       <c r="D10" s="2">
         <v>66</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="E10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="15" t="s">
         <v>11</v>
       </c>
       <c r="G10" s="2">
@@ -892,7 +910,7 @@
       <c r="S10" s="4"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="10">
         <v>281</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -904,10 +922,10 @@
       <c r="D11" s="2">
         <v>43</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="E11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G11" s="2">
@@ -927,7 +945,7 @@
       <c r="S11" s="4"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="A12" s="10">
         <v>284</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -939,10 +957,10 @@
       <c r="D12" s="2">
         <v>53</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="E12" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="15" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="2">
@@ -962,7 +980,7 @@
       <c r="S12" s="4"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="A13" s="10">
         <v>286</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -974,10 +992,10 @@
       <c r="D13" s="2">
         <v>63</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="E13" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G13" s="2">
@@ -997,7 +1015,7 @@
       <c r="S13" s="4"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="A14" s="10">
         <v>287</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1009,10 +1027,10 @@
       <c r="D14" s="2">
         <v>72</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="E14" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2">
@@ -1032,7 +1050,7 @@
       <c r="S14" s="4"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="A15" s="10">
         <v>288</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1044,10 +1062,10 @@
       <c r="D15" s="2">
         <v>31</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
@@ -1067,7 +1085,7 @@
       <c r="S15" s="4"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="A16" s="10">
         <v>289</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1079,10 +1097,10 @@
       <c r="D16" s="2">
         <v>74</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G16" s="2">
@@ -1102,7 +1120,7 @@
       <c r="S16" s="4"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="A17" s="10">
         <v>291</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1114,10 +1132,10 @@
       <c r="D17" s="2">
         <v>72</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="E17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G17" s="2">
@@ -1137,7 +1155,7 @@
       <c r="S17" s="4"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="A18" s="10">
         <v>292</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -1149,10 +1167,10 @@
       <c r="D18" s="2">
         <v>51</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="E18" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G18" s="2">
@@ -1172,7 +1190,7 @@
       <c r="S18" s="4"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="A19" s="10">
         <v>293</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1184,10 +1202,10 @@
       <c r="D19" s="2">
         <v>50</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="2" t="s">
+      <c r="E19" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G19" s="2">
@@ -1207,7 +1225,7 @@
       <c r="S19" s="4"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20" s="10">
         <v>294</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -1219,10 +1237,10 @@
       <c r="D20" s="2">
         <v>44</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G20" s="2">
@@ -1242,7 +1260,7 @@
       <c r="S20" s="4"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="A21" s="10">
         <v>295</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1254,10 +1272,10 @@
       <c r="D21" s="2">
         <v>71</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G21" s="2">
@@ -1277,7 +1295,7 @@
       <c r="S21" s="4"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="A22" s="10">
         <v>296</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1289,10 +1307,10 @@
       <c r="D22" s="2">
         <v>66</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="E22" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G22" s="2">
@@ -1312,7 +1330,7 @@
       <c r="S22" s="4"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="A23" s="10">
         <v>297</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -1324,10 +1342,10 @@
       <c r="D23" s="2">
         <v>77</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="E23" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G23" s="2">
@@ -1347,7 +1365,7 @@
       <c r="S23" s="4"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="A24" s="10">
         <v>298</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -1359,10 +1377,10 @@
       <c r="D24" s="2">
         <v>81</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="E24" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G24" s="2">
@@ -1382,7 +1400,7 @@
       <c r="S24" s="4"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="A25" s="10">
         <v>299</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -1391,10 +1409,10 @@
       <c r="D25" s="2">
         <v>76</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G25" s="2">
@@ -1414,7 +1432,7 @@
       <c r="S25" s="4"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="A26" s="10">
         <v>300</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -1426,10 +1444,10 @@
       <c r="D26" s="2">
         <v>79</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="E26" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G26" s="2">
@@ -1449,7 +1467,7 @@
       <c r="S26" s="4"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="A27" s="10">
         <v>301</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -1461,10 +1479,10 @@
       <c r="D27" s="2">
         <v>57</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="E27" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G27" s="2">
@@ -1484,7 +1502,7 @@
       <c r="S27" s="4"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="A28" s="10">
         <v>302</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -1496,10 +1514,10 @@
       <c r="D28" s="2">
         <v>70</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="15" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="2">
@@ -1519,7 +1537,7 @@
       <c r="S28" s="4"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="A29" s="10">
         <v>304</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -1531,10 +1549,10 @@
       <c r="D29" s="2">
         <v>67</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="E29" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G29" s="2">
@@ -1554,7 +1572,7 @@
       <c r="S29" s="4"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="A30" s="10">
         <v>305</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -1566,10 +1584,10 @@
       <c r="D30" s="2">
         <v>58</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="E30" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="15" t="s">
         <v>18</v>
       </c>
       <c r="G30" s="2">
@@ -1589,7 +1607,7 @@
       <c r="S30" s="4"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="A31" s="10">
         <v>306</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -1601,10 +1619,10 @@
       <c r="D31" s="2">
         <v>56</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="2" t="s">
+      <c r="E31" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="15" t="s">
         <v>11</v>
       </c>
       <c r="G31" s="2">
@@ -1624,7 +1642,7 @@
       <c r="S31" s="4"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="A32" s="10">
         <v>309</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -1633,10 +1651,10 @@
       <c r="D32" s="2">
         <v>61</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="2" t="s">
+      <c r="E32" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G32" s="2">
@@ -1656,7 +1674,7 @@
       <c r="S32" s="4"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="A33" s="10">
         <v>310</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -1668,10 +1686,10 @@
       <c r="D33" s="2">
         <v>65</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="E33" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G33" s="2">
@@ -1691,7 +1709,7 @@
       <c r="S33" s="4"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="A34" s="10">
         <v>312</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -1703,10 +1721,10 @@
       <c r="D34" s="2">
         <v>63</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="2" t="s">
+      <c r="E34" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G34" s="2">
@@ -1726,7 +1744,7 @@
       <c r="S34" s="4"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="A35" s="10">
         <v>313</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -1738,10 +1756,10 @@
       <c r="D35" s="2">
         <v>64</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="E35" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G35" s="2">
@@ -1761,7 +1779,7 @@
       <c r="S35" s="4"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="A36" s="10">
         <v>314</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -1773,10 +1791,10 @@
       <c r="D36" s="2">
         <v>57</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="E36" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G36" s="2">
@@ -1796,7 +1814,7 @@
       <c r="S36" s="4"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="A37" s="10">
         <v>315</v>
       </c>
       <c r="B37" s="2" t="s">
@@ -1808,10 +1826,10 @@
       <c r="D37" s="2">
         <v>72</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G37" s="2">
@@ -1831,7 +1849,7 @@
       <c r="S37" s="4"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="A38" s="10">
         <v>316</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -1843,10 +1861,10 @@
       <c r="D38" s="2">
         <v>65</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="2" t="s">
+      <c r="E38" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G38" s="2">
@@ -1866,7 +1884,7 @@
       <c r="S38" s="4"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+      <c r="A39" s="10">
         <v>317</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -1875,10 +1893,10 @@
       <c r="D39" s="2">
         <v>79</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G39" s="2">
@@ -1898,7 +1916,7 @@
       <c r="S39" s="4"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="A40" s="10">
         <v>318</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -1910,10 +1928,10 @@
       <c r="D40" s="2">
         <v>78</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G40" s="2">
@@ -1933,7 +1951,7 @@
       <c r="S40" s="4"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+      <c r="A41" s="10">
         <v>319</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -1945,10 +1963,10 @@
       <c r="D41" s="2">
         <v>62</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G41" s="2">
@@ -1968,7 +1986,7 @@
       <c r="S41" s="4"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="A42" s="10">
         <v>320</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -1980,10 +1998,10 @@
       <c r="D42" s="2">
         <v>54</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" s="2" t="s">
+      <c r="E42" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G42" s="2">
@@ -2003,7 +2021,7 @@
       <c r="S42" s="4"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="A43" s="10">
         <v>321</v>
       </c>
       <c r="B43" s="2" t="s">
@@ -2015,10 +2033,10 @@
       <c r="D43" s="2">
         <v>47</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G43" s="2">
@@ -2038,7 +2056,7 @@
       <c r="S43" s="4"/>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="A44" s="10">
         <v>322</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -2050,10 +2068,10 @@
       <c r="D44" s="2">
         <v>69</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" s="2" t="s">
+      <c r="E44" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G44" s="2">
@@ -2073,7 +2091,7 @@
       <c r="S44" s="4"/>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+      <c r="A45" s="10">
         <v>323</v>
       </c>
       <c r="B45" s="2" t="s">
@@ -2082,10 +2100,10 @@
       <c r="D45" s="2">
         <v>78</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G45" s="2">
@@ -2105,7 +2123,7 @@
       <c r="S45" s="4"/>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="A46" s="10">
         <v>324</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -2117,10 +2135,10 @@
       <c r="D46" s="2">
         <v>57</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" s="2" t="s">
+      <c r="E46" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G46" s="2">
@@ -2140,7 +2158,7 @@
       <c r="S46" s="4"/>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="A47" s="10">
         <v>325</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -2149,10 +2167,10 @@
       <c r="D47" s="2">
         <v>78</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" s="2" t="s">
+      <c r="E47" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="15" t="s">
         <v>13</v>
       </c>
       <c r="G47" s="2">
@@ -2172,7 +2190,7 @@
       <c r="S47" s="4"/>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="A48" s="10">
         <v>326</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -2184,10 +2202,10 @@
       <c r="D48" s="2">
         <v>58</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G48" s="2">
@@ -2207,7 +2225,7 @@
       <c r="S48" s="4"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="A49" s="10">
         <v>327</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -2219,10 +2237,10 @@
       <c r="D49" s="2">
         <v>61</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" s="2" t="s">
+      <c r="E49" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="2">
@@ -2242,7 +2260,7 @@
       <c r="S49" s="4"/>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="A50" s="10">
         <v>328</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -2251,10 +2269,10 @@
       <c r="D50" s="2">
         <v>71</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G50" s="2">
@@ -2274,7 +2292,7 @@
       <c r="S50" s="4"/>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+      <c r="A51" s="10">
         <v>329</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -2286,10 +2304,10 @@
       <c r="D51" s="2">
         <v>72</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G51" s="2">
@@ -2309,7 +2327,7 @@
       <c r="S51" s="4"/>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+      <c r="A52" s="10">
         <v>330</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -2321,10 +2339,10 @@
       <c r="D52" s="2">
         <v>30</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G52" s="2">
@@ -2344,7 +2362,7 @@
       <c r="S52" s="4"/>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+      <c r="A53" s="10">
         <v>331</v>
       </c>
       <c r="B53" s="2" t="s">
@@ -2356,10 +2374,10 @@
       <c r="D53" s="2">
         <v>76</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" s="2" t="s">
+      <c r="E53" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G53" s="2">
@@ -2379,7 +2397,7 @@
       <c r="S53" s="4"/>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+      <c r="A54" s="10">
         <v>334</v>
       </c>
       <c r="B54" s="2" t="s">
@@ -2391,10 +2409,10 @@
       <c r="D54" s="2">
         <v>67</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" s="2" t="s">
+      <c r="E54" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G54" s="2">
@@ -2414,7 +2432,7 @@
       <c r="S54" s="4"/>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+      <c r="A55" s="10">
         <v>335</v>
       </c>
       <c r="B55" s="2" t="s">
@@ -2423,10 +2441,10 @@
       <c r="D55" s="2">
         <v>76</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E55" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G55" s="2">
@@ -2446,7 +2464,7 @@
       <c r="S55" s="4"/>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+      <c r="A56" s="10">
         <v>336</v>
       </c>
       <c r="B56" s="2" t="s">
@@ -2458,10 +2476,10 @@
       <c r="D56" s="2">
         <v>66</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F56" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G56" s="2">
@@ -2481,7 +2499,7 @@
       <c r="S56" s="4"/>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="A57" s="10">
         <v>337</v>
       </c>
       <c r="B57" s="2" t="s">
@@ -2493,10 +2511,10 @@
       <c r="D57" s="2">
         <v>58</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="F57" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G57" s="2">
@@ -2516,7 +2534,7 @@
       <c r="S57" s="4"/>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+      <c r="A58" s="10">
         <v>338</v>
       </c>
       <c r="C58" s="2" t="s">
@@ -2525,10 +2543,10 @@
       <c r="D58" s="2">
         <v>60</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E58" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F58" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G58" s="2">
@@ -2548,7 +2566,7 @@
       <c r="S58" s="4"/>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
+      <c r="A59" s="10">
         <v>339</v>
       </c>
       <c r="B59" s="2" t="s">
@@ -2560,10 +2578,10 @@
       <c r="D59" s="2">
         <v>65</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" s="2" t="s">
+      <c r="E59" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" s="15" t="s">
         <v>17</v>
       </c>
       <c r="G59" s="2">
@@ -2583,7 +2601,7 @@
       <c r="S59" s="4"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+      <c r="A60" s="10">
         <v>340</v>
       </c>
       <c r="B60" s="2" t="s">
@@ -2595,10 +2613,10 @@
       <c r="D60" s="2">
         <v>29</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" s="2" t="s">
+      <c r="E60" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G60" s="2">
@@ -2618,7 +2636,7 @@
       <c r="S60" s="4"/>
     </row>
     <row r="61" spans="1:19" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="2">
+      <c r="A61" s="10">
         <v>341</v>
       </c>
       <c r="B61" s="2" t="s">
@@ -2630,10 +2648,10 @@
       <c r="D61" s="2">
         <v>57</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E61" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="F61" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G61" s="2">
@@ -2653,22 +2671,22 @@
       <c r="S61" s="4"/>
     </row>
     <row r="62" spans="1:19" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="9">
+      <c r="A62" s="12">
         <v>342</v>
       </c>
-      <c r="B62" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C62" s="9" t="s">
+      <c r="B62" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="2">
         <v>37</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" s="2" t="s">
+      <c r="E62" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G62" s="2">
@@ -2688,22 +2706,22 @@
       <c r="S62" s="4"/>
     </row>
     <row r="63" spans="1:19" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="9">
+      <c r="A63" s="12">
         <v>345</v>
       </c>
-      <c r="B63" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C63" s="9" t="s">
+      <c r="B63" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="2">
         <v>34</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" s="2" t="s">
+      <c r="E63" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" s="15" t="s">
         <v>17</v>
       </c>
       <c r="G63" s="2">
@@ -2723,7 +2741,7 @@
       <c r="S63" s="4"/>
     </row>
     <row r="64" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="6">
+      <c r="A64" s="11">
         <v>383</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -2732,10 +2750,10 @@
       <c r="C64" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" s="2" t="s">
+      <c r="E64" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H64" s="5">
@@ -2752,7 +2770,7 @@
       <c r="S64" s="4"/>
     </row>
     <row r="65" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="6">
+      <c r="A65" s="11">
         <v>387</v>
       </c>
       <c r="B65" s="6" t="s">
@@ -2761,10 +2779,10 @@
       <c r="C65" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" s="2" t="s">
+      <c r="E65" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H65" s="5">
@@ -2781,7 +2799,7 @@
       <c r="S65" s="4"/>
     </row>
     <row r="66" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="6">
+      <c r="A66" s="11">
         <v>390</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -2790,10 +2808,10 @@
       <c r="C66" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" s="2" t="s">
+      <c r="E66" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H66" s="5">
@@ -2810,7 +2828,7 @@
       <c r="S66" s="4"/>
     </row>
     <row r="67" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="6">
+      <c r="A67" s="11">
         <v>391</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -2819,10 +2837,10 @@
       <c r="C67" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F67" s="2" t="s">
+      <c r="E67" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F67" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H67" s="5">
@@ -2839,7 +2857,7 @@
       <c r="S67" s="4"/>
     </row>
     <row r="68" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="6">
+      <c r="A68" s="11">
         <v>392</v>
       </c>
       <c r="B68" s="6" t="s">
@@ -2848,10 +2866,10 @@
       <c r="C68" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="E68" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F68" s="2" t="s">
+      <c r="F68" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H68" s="5">
@@ -2868,7 +2886,7 @@
       <c r="S68" s="4"/>
     </row>
     <row r="69" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="6">
+      <c r="A69" s="11">
         <v>393</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -2877,10 +2895,10 @@
       <c r="C69" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" s="2" t="s">
+      <c r="E69" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H69" s="5">
@@ -2897,7 +2915,7 @@
       <c r="S69" s="4"/>
     </row>
     <row r="70" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="6">
+      <c r="A70" s="11">
         <v>394</v>
       </c>
       <c r="B70" s="6" t="s">
@@ -2906,10 +2924,10 @@
       <c r="C70" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" s="2" t="s">
+      <c r="E70" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H70" s="5">
@@ -2926,7 +2944,7 @@
       <c r="S70" s="4"/>
     </row>
     <row r="71" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="6">
+      <c r="A71" s="11">
         <v>395</v>
       </c>
       <c r="B71" s="6" t="s">
@@ -2935,10 +2953,10 @@
       <c r="C71" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" s="2" t="s">
+      <c r="E71" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H71" s="5">
@@ -2955,7 +2973,7 @@
       <c r="S71" s="4"/>
     </row>
     <row r="72" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="6">
+      <c r="A72" s="11">
         <v>396</v>
       </c>
       <c r="B72" s="6" t="s">
@@ -2964,10 +2982,10 @@
       <c r="C72" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" s="2" t="s">
+      <c r="E72" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H72" s="5">
@@ -2984,7 +3002,7 @@
       <c r="S72" s="4"/>
     </row>
     <row r="73" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="6">
+      <c r="A73" s="11">
         <v>398</v>
       </c>
       <c r="B73" s="6" t="s">
@@ -2993,10 +3011,10 @@
       <c r="C73" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" s="2" t="s">
+      <c r="E73" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" s="15" t="s">
         <v>17</v>
       </c>
       <c r="H73" s="5">
@@ -3013,7 +3031,7 @@
       <c r="S73" s="4"/>
     </row>
     <row r="74" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="6">
+      <c r="A74" s="11">
         <v>399</v>
       </c>
       <c r="B74" s="6" t="s">
@@ -3022,10 +3040,10 @@
       <c r="C74" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" s="2" t="s">
+      <c r="E74" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" s="15" t="s">
         <v>17</v>
       </c>
       <c r="H74" s="5">
@@ -3042,15 +3060,15 @@
       <c r="S74" s="4"/>
     </row>
     <row r="75" spans="1:19" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="10">
+      <c r="A75" s="12">
         <v>401</v>
       </c>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="E75" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" s="2" t="s">
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="E75" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H75" s="2">
@@ -3067,7 +3085,7 @@
       <c r="S75" s="4"/>
     </row>
     <row r="76" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="6">
+      <c r="A76" s="11">
         <v>402</v>
       </c>
       <c r="B76" s="6" t="s">
@@ -3076,10 +3094,10 @@
       <c r="C76" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" s="2" t="s">
+      <c r="E76" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F76" s="15" t="s">
         <v>17</v>
       </c>
       <c r="H76" s="5">
@@ -3096,7 +3114,7 @@
       <c r="S76" s="4"/>
     </row>
     <row r="77" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="6">
+      <c r="A77" s="11">
         <v>403</v>
       </c>
       <c r="B77" s="6" t="s">
@@ -3105,10 +3123,10 @@
       <c r="C77" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" s="2" t="s">
+      <c r="E77" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H77" s="5">
@@ -3125,7 +3143,7 @@
       <c r="S77" s="4"/>
     </row>
     <row r="78" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="6">
+      <c r="A78" s="11">
         <v>404</v>
       </c>
       <c r="B78" s="6" t="s">
@@ -3134,10 +3152,10 @@
       <c r="C78" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="E78" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="F78" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H78" s="5">
@@ -3154,7 +3172,7 @@
       <c r="S78" s="4"/>
     </row>
     <row r="79" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="6">
+      <c r="A79" s="11">
         <v>405</v>
       </c>
       <c r="B79" s="6" t="s">
@@ -3163,10 +3181,10 @@
       <c r="C79" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F79" s="2" t="s">
+      <c r="E79" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H79" s="5">
@@ -3183,7 +3201,7 @@
       <c r="S79" s="4"/>
     </row>
     <row r="80" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="6">
+      <c r="A80" s="11">
         <v>406</v>
       </c>
       <c r="B80" s="6" t="s">
@@ -3192,10 +3210,10 @@
       <c r="C80" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" s="2" t="s">
+      <c r="E80" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H80" s="5">
@@ -3212,7 +3230,7 @@
       <c r="S80" s="4"/>
     </row>
     <row r="81" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="6">
+      <c r="A81" s="11">
         <v>407</v>
       </c>
       <c r="B81" s="6" t="s">
@@ -3221,10 +3239,10 @@
       <c r="C81" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F81" s="2" t="s">
+      <c r="E81" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" s="15" t="s">
         <v>17</v>
       </c>
       <c r="H81" s="5">
@@ -3241,19 +3259,19 @@
       <c r="S81" s="4"/>
     </row>
     <row r="82" spans="1:19" ht="20" x14ac:dyDescent="0.25">
-      <c r="A82" s="8">
+      <c r="A82" s="13">
         <v>408</v>
       </c>
-      <c r="B82" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F82" s="2" t="s">
+      <c r="B82" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H82" s="5">
@@ -3270,19 +3288,19 @@
       <c r="S82" s="4"/>
     </row>
     <row r="83" spans="1:19" ht="20" x14ac:dyDescent="0.25">
-      <c r="A83" s="8">
+      <c r="A83" s="13">
         <v>409</v>
       </c>
-      <c r="B83" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" s="2" t="s">
+      <c r="B83" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H83" s="5">
@@ -3299,19 +3317,19 @@
       <c r="S83" s="4"/>
     </row>
     <row r="84" spans="1:19" ht="20" x14ac:dyDescent="0.25">
-      <c r="A84" s="8">
+      <c r="A84" s="13">
         <v>410</v>
       </c>
-      <c r="B84" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E84" s="2" t="s">
+      <c r="B84" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F84" s="2" t="s">
+      <c r="F84" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H84" s="5">
@@ -3328,13 +3346,13 @@
       <c r="S84" s="4"/>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A85" s="7">
+      <c r="A85" s="10">
         <v>411</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F85" s="2" t="s">
+      <c r="E85" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H85" s="2">
@@ -3351,13 +3369,13 @@
       <c r="S85" s="4"/>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A86" s="7">
+      <c r="A86" s="10">
         <v>413</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" s="2" t="s">
+      <c r="E86" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H86" s="2">
@@ -3374,13 +3392,13 @@
       <c r="S86" s="4"/>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A87" s="7">
+      <c r="A87" s="10">
         <v>415</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="E87" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F87" s="2" t="s">
+      <c r="F87" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H87" s="2">
@@ -3397,13 +3415,13 @@
       <c r="S87" s="4"/>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A88" s="7">
+      <c r="A88" s="10">
         <v>416</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F88" s="2" t="s">
+      <c r="E88" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H88" s="2">
@@ -3420,13 +3438,13 @@
       <c r="S88" s="4"/>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A89" s="7">
+      <c r="A89" s="10">
         <v>417</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F89" s="2" t="s">
+      <c r="E89" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F89" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H89" s="2">
@@ -3443,13 +3461,13 @@
       <c r="S89" s="4"/>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A90" s="7">
+      <c r="A90" s="10">
         <v>418</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F90" s="2" t="s">
+      <c r="E90" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H90" s="2">
@@ -3466,13 +3484,13 @@
       <c r="S90" s="4"/>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A91" s="7">
+      <c r="A91" s="10">
         <v>418</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F91" s="2" t="s">
+      <c r="E91" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H91" s="2">
@@ -3489,13 +3507,13 @@
       <c r="S91" s="4"/>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A92" s="7">
+      <c r="A92" s="10">
         <v>419</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="E92" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F92" s="2" t="s">
+      <c r="F92" s="15" t="s">
         <v>16</v>
       </c>
       <c r="H92" s="2">
@@ -3512,13 +3530,13 @@
       <c r="S92" s="4"/>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A93" s="7">
+      <c r="A93" s="10">
         <v>420</v>
       </c>
-      <c r="E93" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F93" s="2" t="s">
+      <c r="E93" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F93" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H93" s="2">
@@ -3535,13 +3553,13 @@
       <c r="S93" s="4"/>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A94" s="7">
+      <c r="A94" s="10">
         <v>421</v>
       </c>
-      <c r="E94" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F94" s="2" t="s">
+      <c r="E94" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F94" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H94" s="2">
@@ -3558,13 +3576,13 @@
       <c r="S94" s="4"/>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A95" s="7">
+      <c r="A95" s="10">
         <v>424</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="E95" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F95" s="2" t="s">
+      <c r="F95" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H95" s="2">
@@ -3581,13 +3599,13 @@
       <c r="S95" s="4"/>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A96" s="7">
+      <c r="A96" s="10">
         <v>425</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="E96" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F96" s="2" t="s">
+      <c r="F96" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H96" s="2">
@@ -3604,13 +3622,13 @@
       <c r="S96" s="4"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A97" s="7">
+      <c r="A97" s="10">
         <v>426</v>
       </c>
-      <c r="E97" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F97" s="2" t="s">
+      <c r="E97" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F97" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H97" s="2">
@@ -3627,13 +3645,13 @@
       <c r="S97" s="4"/>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A98" s="7">
+      <c r="A98" s="10">
         <v>427</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F98" s="2" t="s">
+      <c r="E98" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F98" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H98" s="2">
@@ -3650,13 +3668,13 @@
       <c r="S98" s="4"/>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A99" s="7">
+      <c r="A99" s="10">
         <v>428</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F99" s="2" t="s">
+      <c r="E99" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F99" s="15" t="s">
         <v>16</v>
       </c>
       <c r="H99" s="2">
@@ -3673,13 +3691,13 @@
       <c r="S99" s="4"/>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A100" s="7">
+      <c r="A100" s="10">
         <v>429</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F100" s="2" t="s">
+      <c r="E100" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F100" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H100" s="2">
@@ -3696,13 +3714,13 @@
       <c r="S100" s="4"/>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A101" s="7">
+      <c r="A101" s="10">
         <v>430</v>
       </c>
-      <c r="E101" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F101" s="2" t="s">
+      <c r="E101" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F101" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H101" s="2">
@@ -3719,13 +3737,13 @@
       <c r="S101" s="4"/>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A102" s="7">
+      <c r="A102" s="10">
         <v>431</v>
       </c>
-      <c r="E102" s="2" t="s">
+      <c r="E102" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F102" s="2" t="s">
+      <c r="F102" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H102" s="2">
@@ -3742,13 +3760,13 @@
       <c r="S102" s="4"/>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A103" s="7">
+      <c r="A103" s="10">
         <v>432</v>
       </c>
-      <c r="E103" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F103" s="2" t="s">
+      <c r="E103" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F103" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H103" s="2">
@@ -3765,13 +3783,13 @@
       <c r="S103" s="4"/>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A104" s="7">
+      <c r="A104" s="10">
         <v>433</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F104" s="2" t="s">
+      <c r="E104" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F104" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H104" s="2">
@@ -3788,13 +3806,13 @@
       <c r="S104" s="4"/>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A105" s="7">
+      <c r="A105" s="10">
         <v>434</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F105" s="2" t="s">
+      <c r="E105" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F105" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H105" s="2">
@@ -3811,13 +3829,13 @@
       <c r="S105" s="4"/>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A106" s="7">
+      <c r="A106" s="10">
         <v>435</v>
       </c>
-      <c r="E106" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F106" s="2" t="s">
+      <c r="E106" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F106" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H106" s="2">
@@ -3834,13 +3852,13 @@
       <c r="S106" s="4"/>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A107" s="7">
+      <c r="A107" s="10">
         <v>436</v>
       </c>
-      <c r="E107" s="2" t="s">
+      <c r="E107" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F107" s="2" t="s">
+      <c r="F107" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H107" s="2">
@@ -3857,13 +3875,13 @@
       <c r="S107" s="4"/>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A108" s="7">
+      <c r="A108" s="10">
         <v>437</v>
       </c>
-      <c r="E108" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F108" s="2" t="s">
+      <c r="E108" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F108" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H108" s="2">
@@ -3880,13 +3898,13 @@
       <c r="S108" s="4"/>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A109" s="7">
+      <c r="A109" s="10">
         <v>438</v>
       </c>
-      <c r="E109" s="2" t="s">
+      <c r="E109" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F109" s="2" t="s">
+      <c r="F109" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H109" s="2">
@@ -3903,13 +3921,13 @@
       <c r="S109" s="4"/>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A110" s="7">
+      <c r="A110" s="10">
         <v>439</v>
       </c>
-      <c r="E110" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F110" s="2" t="s">
+      <c r="E110" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F110" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H110" s="2">
@@ -3926,13 +3944,13 @@
       <c r="S110" s="4"/>
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A111" s="7">
+      <c r="A111" s="10">
         <v>439</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F111" s="2" t="s">
+      <c r="E111" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F111" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H111" s="2">
@@ -3949,13 +3967,13 @@
       <c r="S111" s="4"/>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A112" s="7">
+      <c r="A112" s="10">
         <v>440</v>
       </c>
-      <c r="E112" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F112" s="2" t="s">
+      <c r="E112" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F112" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H112" s="2">
@@ -3972,13 +3990,13 @@
       <c r="S112" s="4"/>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A113" s="7">
+      <c r="A113" s="10">
         <v>441</v>
       </c>
-      <c r="E113" s="2" t="s">
+      <c r="E113" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F113" s="2" t="s">
+      <c r="F113" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H113" s="2">
@@ -3995,13 +4013,13 @@
       <c r="S113" s="4"/>
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A114" s="7">
+      <c r="A114" s="10">
         <v>442</v>
       </c>
-      <c r="E114" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F114" s="2" t="s">
+      <c r="E114" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F114" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H114" s="2">
@@ -4018,13 +4036,13 @@
       <c r="S114" s="4"/>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A115" s="7">
+      <c r="A115" s="10">
         <v>443</v>
       </c>
-      <c r="E115" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F115" s="2" t="s">
+      <c r="E115" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F115" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H115" s="2">
@@ -4041,13 +4059,13 @@
       <c r="S115" s="4"/>
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A116" s="7">
+      <c r="A116" s="10">
         <v>444</v>
       </c>
-      <c r="E116" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F116" s="2" t="s">
+      <c r="E116" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F116" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H116" s="2">
@@ -4064,13 +4082,13 @@
       <c r="S116" s="4"/>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A117" s="7">
+      <c r="A117" s="10">
         <v>445</v>
       </c>
-      <c r="E117" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F117" s="2" t="s">
+      <c r="E117" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F117" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H117" s="2">
@@ -4087,13 +4105,13 @@
       <c r="S117" s="4"/>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A118" s="7">
+      <c r="A118" s="10">
         <v>446</v>
       </c>
-      <c r="E118" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F118" s="2" t="s">
+      <c r="E118" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F118" s="15" t="s">
         <v>13</v>
       </c>
       <c r="H118" s="2">
@@ -4110,13 +4128,13 @@
       <c r="S118" s="4"/>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A119" s="7">
+      <c r="A119" s="10">
         <v>448</v>
       </c>
-      <c r="E119" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F119" s="2" t="s">
+      <c r="E119" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F119" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H119" s="2">
@@ -4133,13 +4151,13 @@
       <c r="S119" s="4"/>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A120" s="7">
+      <c r="A120" s="10">
         <v>449</v>
       </c>
-      <c r="E120" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F120" s="2" t="s">
+      <c r="E120" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F120" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H120" s="2">
@@ -4156,13 +4174,13 @@
       <c r="S120" s="4"/>
     </row>
     <row r="121" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A121" s="7">
+      <c r="A121" s="10">
         <v>450</v>
       </c>
-      <c r="E121" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F121" s="2" t="s">
+      <c r="E121" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F121" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H121" s="2">
@@ -4179,13 +4197,13 @@
       <c r="S121" s="4"/>
     </row>
     <row r="122" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A122" s="7">
+      <c r="A122" s="10">
         <v>451</v>
       </c>
-      <c r="E122" s="2" t="s">
+      <c r="E122" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F122" s="2" t="s">
+      <c r="F122" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H122" s="2">
@@ -4202,13 +4220,13 @@
       <c r="S122" s="4"/>
     </row>
     <row r="123" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A123" s="7">
+      <c r="A123" s="10">
         <v>452</v>
       </c>
-      <c r="E123" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F123" s="2" t="s">
+      <c r="E123" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F123" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H123" s="2">
@@ -4225,13 +4243,13 @@
       <c r="S123" s="4"/>
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A124" s="7">
+      <c r="A124" s="10">
         <v>454</v>
       </c>
-      <c r="E124" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F124" s="2" t="s">
+      <c r="E124" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F124" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H124" s="2">
@@ -4248,13 +4266,13 @@
       <c r="S124" s="4"/>
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A125" s="7">
+      <c r="A125" s="10">
         <v>455</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="E125" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F125" s="2" t="s">
+      <c r="F125" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H125" s="2">
@@ -4271,13 +4289,13 @@
       <c r="S125" s="4"/>
     </row>
     <row r="126" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A126" s="7">
+      <c r="A126" s="10">
         <v>456</v>
       </c>
-      <c r="E126" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F126" s="2" t="s">
+      <c r="E126" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F126" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H126" s="2">
@@ -4294,13 +4312,13 @@
       <c r="S126" s="4"/>
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A127" s="7">
+      <c r="A127" s="10">
         <v>458</v>
       </c>
-      <c r="E127" s="2" t="s">
+      <c r="E127" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F127" s="2" t="s">
+      <c r="F127" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H127" s="2">
@@ -4317,13 +4335,13 @@
       <c r="S127" s="4"/>
     </row>
     <row r="128" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A128" s="7">
+      <c r="A128" s="10">
         <v>459</v>
       </c>
-      <c r="E128" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F128" s="2" t="s">
+      <c r="E128" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F128" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H128" s="2">
@@ -4340,13 +4358,13 @@
       <c r="S128" s="4"/>
     </row>
     <row r="129" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A129" s="7">
+      <c r="A129" s="10">
         <v>462</v>
       </c>
-      <c r="E129" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F129" s="2" t="s">
+      <c r="E129" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F129" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H129" s="2">
@@ -4363,13 +4381,13 @@
       <c r="S129" s="4"/>
     </row>
     <row r="130" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A130" s="7">
+      <c r="A130" s="10">
         <v>465</v>
       </c>
-      <c r="E130" s="2" t="s">
+      <c r="E130" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F130" s="2" t="s">
+      <c r="F130" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H130" s="2">
@@ -4386,13 +4404,13 @@
       <c r="S130" s="4"/>
     </row>
     <row r="131" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A131" s="7">
+      <c r="A131" s="10">
         <v>468</v>
       </c>
-      <c r="E131" s="2" t="s">
+      <c r="E131" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F131" s="2" t="s">
+      <c r="F131" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H131" s="2">
@@ -4409,13 +4427,13 @@
       <c r="S131" s="4"/>
     </row>
     <row r="132" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A132" s="7">
+      <c r="A132" s="10">
         <v>471</v>
       </c>
-      <c r="E132" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F132" s="2" t="s">
+      <c r="E132" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F132" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H132" s="2">
@@ -4432,13 +4450,13 @@
       <c r="S132" s="4"/>
     </row>
     <row r="133" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A133" s="7">
+      <c r="A133" s="10">
         <v>472</v>
       </c>
-      <c r="E133" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F133" s="2" t="s">
+      <c r="E133" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F133" s="15" t="s">
         <v>11</v>
       </c>
       <c r="H133" s="2">
@@ -4455,13 +4473,13 @@
       <c r="S133" s="4"/>
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A134" s="7">
+      <c r="A134" s="10">
         <v>473</v>
       </c>
-      <c r="E134" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F134" s="2" t="s">
+      <c r="E134" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F134" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H134" s="2">
@@ -4478,13 +4496,13 @@
       <c r="S134" s="4"/>
     </row>
     <row r="135" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A135" s="7">
+      <c r="A135" s="10">
         <v>474</v>
       </c>
-      <c r="E135" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F135" s="2" t="s">
+      <c r="E135" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F135" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H135" s="2">
@@ -4501,13 +4519,13 @@
       <c r="S135" s="4"/>
     </row>
     <row r="136" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A136" s="7">
+      <c r="A136" s="10">
         <v>477</v>
       </c>
-      <c r="E136" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F136" s="2" t="s">
+      <c r="E136" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F136" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H136" s="2">
@@ -4524,13 +4542,13 @@
       <c r="S136" s="4"/>
     </row>
     <row r="137" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A137" s="7">
+      <c r="A137" s="10">
         <v>478</v>
       </c>
-      <c r="E137" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F137" s="2" t="s">
+      <c r="E137" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F137" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H137" s="2">
@@ -4547,13 +4565,13 @@
       <c r="S137" s="4"/>
     </row>
     <row r="138" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A138" s="7">
+      <c r="A138" s="10">
         <v>479</v>
       </c>
-      <c r="E138" s="2" t="s">
+      <c r="E138" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F138" s="2" t="s">
+      <c r="F138" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H138" s="2">
@@ -4570,13 +4588,13 @@
       <c r="S138" s="4"/>
     </row>
     <row r="139" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A139" s="7">
+      <c r="A139" s="10">
         <v>482</v>
       </c>
-      <c r="E139" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F139" s="2" t="s">
+      <c r="E139" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F139" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H139" s="2">
@@ -4593,13 +4611,13 @@
       <c r="S139" s="4"/>
     </row>
     <row r="140" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A140" s="7">
+      <c r="A140" s="10">
         <v>483</v>
       </c>
-      <c r="E140" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F140" s="2" t="s">
+      <c r="E140" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F140" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H140" s="2">
@@ -4616,13 +4634,13 @@
       <c r="S140" s="4"/>
     </row>
     <row r="141" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A141" s="7">
+      <c r="A141" s="10">
         <v>484</v>
       </c>
-      <c r="E141" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F141" s="2" t="s">
+      <c r="E141" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F141" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H141" s="2">
@@ -4639,13 +4657,13 @@
       <c r="S141" s="4"/>
     </row>
     <row r="142" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A142" s="7">
+      <c r="A142" s="10">
         <v>485</v>
       </c>
-      <c r="E142" s="2" t="s">
+      <c r="E142" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F142" s="2" t="s">
+      <c r="F142" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H142" s="2">
@@ -4660,13 +4678,13 @@
       </c>
     </row>
     <row r="143" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A143" s="7">
+      <c r="A143" s="10">
         <v>487</v>
       </c>
-      <c r="E143" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F143" s="2" t="s">
+      <c r="E143" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F143" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H143" s="2">
@@ -4681,13 +4699,13 @@
       </c>
     </row>
     <row r="144" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A144" s="7">
+      <c r="A144" s="10">
         <v>488</v>
       </c>
-      <c r="E144" s="2" t="s">
+      <c r="E144" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F144" s="2" t="s">
+      <c r="F144" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H144" s="2">
@@ -4702,13 +4720,13 @@
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A145" s="7">
+      <c r="A145" s="10">
         <v>489</v>
       </c>
-      <c r="E145" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F145" s="2" t="s">
+      <c r="E145" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F145" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H145" s="2">
@@ -4723,13 +4741,13 @@
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" s="7">
+      <c r="A146" s="10">
         <v>490</v>
       </c>
-      <c r="E146" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F146" s="2" t="s">
+      <c r="E146" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F146" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H146" s="2">
@@ -4744,13 +4762,13 @@
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A147" s="7">
+      <c r="A147" s="10">
         <v>491</v>
       </c>
-      <c r="E147" s="2" t="s">
+      <c r="E147" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F147" s="2" t="s">
+      <c r="F147" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H147" s="2">
@@ -4765,13 +4783,13 @@
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A148" s="7">
+      <c r="A148" s="10">
         <v>493</v>
       </c>
-      <c r="E148" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F148" s="2" t="s">
+      <c r="E148" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F148" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H148" s="2">
@@ -4786,13 +4804,13 @@
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A149" s="7">
+      <c r="A149" s="10">
         <v>494</v>
       </c>
-      <c r="E149" s="2" t="s">
+      <c r="E149" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F149" s="2" t="s">
+      <c r="F149" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H149" s="2">
@@ -4807,13 +4825,13 @@
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A150" s="7">
+      <c r="A150" s="10">
         <v>498</v>
       </c>
-      <c r="E150" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F150" s="2" t="s">
+      <c r="E150" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F150" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H150" s="2">
@@ -4828,13 +4846,13 @@
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A151" s="7">
+      <c r="A151" s="10">
         <v>499</v>
       </c>
-      <c r="E151" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F151" s="2" t="s">
+      <c r="E151" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F151" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H151" s="2">
@@ -4849,13 +4867,13 @@
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A152" s="7">
+      <c r="A152" s="10">
         <v>500</v>
       </c>
-      <c r="E152" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F152" s="2" t="s">
+      <c r="E152" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F152" s="15" t="s">
         <v>17</v>
       </c>
       <c r="H152" s="2">
@@ -4870,13 +4888,13 @@
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A153" s="7">
+      <c r="A153" s="10">
         <v>501</v>
       </c>
-      <c r="E153" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F153" s="2" t="s">
+      <c r="E153" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F153" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H153" s="2">
@@ -4891,13 +4909,13 @@
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A154" s="7">
+      <c r="A154" s="10">
         <v>502</v>
       </c>
-      <c r="E154" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F154" s="2" t="s">
+      <c r="E154" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F154" s="15" t="s">
         <v>18</v>
       </c>
       <c r="H154" s="2">
@@ -4912,13 +4930,13 @@
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A155" s="7">
+      <c r="A155" s="10">
         <v>505</v>
       </c>
-      <c r="E155" s="2" t="s">
+      <c r="E155" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F155" s="2" t="s">
+      <c r="F155" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H155" s="2">
@@ -4933,13 +4951,13 @@
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A156" s="7">
+      <c r="A156" s="10">
         <v>506</v>
       </c>
-      <c r="E156" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F156" s="2" t="s">
+      <c r="E156" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F156" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H156" s="2">
@@ -4954,13 +4972,13 @@
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A157" s="7">
+      <c r="A157" s="10">
         <v>508</v>
       </c>
-      <c r="E157" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F157" s="2" t="s">
+      <c r="E157" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F157" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H157" s="2">
@@ -4975,13 +4993,13 @@
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A158" s="7">
+      <c r="A158" s="10">
         <v>509</v>
       </c>
-      <c r="E158" s="2" t="s">
+      <c r="E158" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F158" s="2" t="s">
+      <c r="F158" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H158" s="2">
@@ -4996,13 +5014,13 @@
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A159" s="7">
+      <c r="A159" s="10">
         <v>510</v>
       </c>
-      <c r="E159" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F159" s="2" t="s">
+      <c r="E159" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F159" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H159" s="2">
@@ -5017,13 +5035,13 @@
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A160" s="7">
+      <c r="A160" s="10">
         <v>511</v>
       </c>
-      <c r="E160" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F160" s="2" t="s">
+      <c r="E160" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F160" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H160" s="2">
@@ -5038,13 +5056,13 @@
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A161" s="7">
+      <c r="A161" s="10">
         <v>512</v>
       </c>
-      <c r="E161" s="2" t="s">
+      <c r="E161" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F161" s="2" t="s">
+      <c r="F161" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H161" s="2">
@@ -5059,13 +5077,13 @@
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A162" s="7">
+      <c r="A162" s="10">
         <v>514</v>
       </c>
-      <c r="E162" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F162" s="2" t="s">
+      <c r="E162" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H162" s="2">
@@ -5080,13 +5098,13 @@
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A163" s="7">
+      <c r="A163" s="10">
         <v>515</v>
       </c>
-      <c r="E163" s="2" t="s">
+      <c r="E163" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F163" s="2" t="s">
+      <c r="F163" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H163" s="2">
@@ -5101,13 +5119,13 @@
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" s="7">
+      <c r="A164" s="10">
         <v>516</v>
       </c>
-      <c r="E164" s="2" t="s">
+      <c r="E164" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F164" s="2" t="s">
+      <c r="F164" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H164" s="2">
@@ -5122,13 +5140,13 @@
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A165" s="7">
+      <c r="A165" s="10">
         <v>517</v>
       </c>
-      <c r="E165" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F165" s="2" t="s">
+      <c r="E165" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F165" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H165" s="2">
@@ -5143,13 +5161,13 @@
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A166" s="7">
+      <c r="A166" s="10">
         <v>518</v>
       </c>
-      <c r="E166" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F166" s="2" t="s">
+      <c r="E166" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F166" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H166" s="2">
@@ -5164,13 +5182,13 @@
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A167" s="7">
+      <c r="A167" s="10">
         <v>519</v>
       </c>
-      <c r="E167" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F167" s="2" t="s">
+      <c r="E167" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F167" s="15" t="s">
         <v>13</v>
       </c>
       <c r="H167" s="2">
@@ -5185,13 +5203,13 @@
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A168" s="7">
+      <c r="A168" s="10">
         <v>520</v>
       </c>
-      <c r="E168" s="2" t="s">
+      <c r="E168" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F168" s="2" t="s">
+      <c r="F168" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H168" s="2">
@@ -5206,13 +5224,13 @@
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A169" s="7">
+      <c r="A169" s="10">
         <v>521</v>
       </c>
-      <c r="E169" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F169" s="2" t="s">
+      <c r="E169" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F169" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H169" s="2">
@@ -5227,13 +5245,13 @@
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A170" s="7">
+      <c r="A170" s="10">
         <v>522</v>
       </c>
-      <c r="E170" s="2" t="s">
+      <c r="E170" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F170" s="2" t="s">
+      <c r="F170" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H170" s="2">
@@ -5248,13 +5266,13 @@
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A171" s="7">
+      <c r="A171" s="10">
         <v>523</v>
       </c>
-      <c r="E171" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F171" s="2" t="s">
+      <c r="E171" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F171" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H171" s="2">
@@ -5269,13 +5287,13 @@
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A172" s="7">
+      <c r="A172" s="10">
         <v>524</v>
       </c>
-      <c r="E172" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F172" s="2" t="s">
+      <c r="E172" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F172" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H172" s="2">
@@ -5290,13 +5308,13 @@
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A173" s="7">
+      <c r="A173" s="10">
         <v>526</v>
       </c>
-      <c r="E173" s="2" t="s">
+      <c r="E173" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F173" s="2" t="s">
+      <c r="F173" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H173" s="2">
@@ -5311,13 +5329,13 @@
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A174" s="7">
+      <c r="A174" s="10">
         <v>528</v>
       </c>
-      <c r="E174" s="2" t="s">
+      <c r="E174" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F174" s="2" t="s">
+      <c r="F174" s="15" t="s">
         <v>13</v>
       </c>
       <c r="H174" s="2">
@@ -5332,13 +5350,13 @@
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A175" s="7">
+      <c r="A175" s="10">
         <v>529</v>
       </c>
-      <c r="E175" s="2" t="s">
+      <c r="E175" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F175" s="2" t="s">
+      <c r="F175" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H175" s="2">
@@ -5353,13 +5371,13 @@
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A176" s="7">
+      <c r="A176" s="10">
         <v>530</v>
       </c>
-      <c r="E176" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F176" s="2" t="s">
+      <c r="E176" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F176" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H176" s="2">
@@ -5374,13 +5392,13 @@
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A177" s="7">
+      <c r="A177" s="10">
         <v>531</v>
       </c>
-      <c r="E177" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F177" s="2" t="s">
+      <c r="E177" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F177" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H177" s="2">
@@ -5395,13 +5413,13 @@
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A178" s="7">
+      <c r="A178" s="10">
         <v>533</v>
       </c>
-      <c r="E178" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F178" s="2" t="s">
+      <c r="E178" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F178" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H178" s="2">
@@ -5416,13 +5434,13 @@
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A179" s="7">
+      <c r="A179" s="10">
         <v>534</v>
       </c>
-      <c r="E179" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F179" s="2" t="s">
+      <c r="E179" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F179" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H179" s="2">
@@ -5437,13 +5455,13 @@
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A180" s="7">
+      <c r="A180" s="10">
         <v>536</v>
       </c>
-      <c r="E180" s="2" t="s">
+      <c r="E180" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F180" s="2" t="s">
+      <c r="F180" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H180" s="2">
@@ -5458,13 +5476,13 @@
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A181" s="7">
+      <c r="A181" s="10">
         <v>537</v>
       </c>
-      <c r="E181" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F181" s="2" t="s">
+      <c r="E181" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F181" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H181" s="2">
@@ -5479,13 +5497,13 @@
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A182" s="7">
+      <c r="A182" s="10">
         <v>538</v>
       </c>
-      <c r="E182" s="2" t="s">
+      <c r="E182" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F182" s="2" t="s">
+      <c r="F182" s="15" t="s">
         <v>18</v>
       </c>
       <c r="H182" s="2">
@@ -5500,13 +5518,13 @@
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A183" s="7">
+      <c r="A183" s="10">
         <v>539</v>
       </c>
-      <c r="E183" s="2" t="s">
+      <c r="E183" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F183" s="2" t="s">
+      <c r="F183" s="15" t="s">
         <v>13</v>
       </c>
       <c r="H183" s="2">
@@ -5521,13 +5539,13 @@
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A184" s="7">
+      <c r="A184" s="10">
         <v>540</v>
       </c>
-      <c r="E184" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F184" s="2" t="s">
+      <c r="E184" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F184" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H184" s="2">
@@ -5542,13 +5560,13 @@
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A185" s="7">
+      <c r="A185" s="10">
         <v>544</v>
       </c>
-      <c r="E185" s="2" t="s">
+      <c r="E185" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F185" s="2" t="s">
+      <c r="F185" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H185" s="2">
@@ -5563,13 +5581,13 @@
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A186" s="7">
+      <c r="A186" s="10">
         <v>545</v>
       </c>
-      <c r="E186" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F186" s="2" t="s">
+      <c r="E186" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F186" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H186" s="2">
@@ -5584,13 +5602,13 @@
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A187" s="7">
+      <c r="A187" s="10">
         <v>546</v>
       </c>
-      <c r="E187" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F187" s="2" t="s">
+      <c r="E187" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F187" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H187" s="2">
@@ -5605,13 +5623,13 @@
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A188" s="7">
+      <c r="A188" s="10">
         <v>548</v>
       </c>
-      <c r="E188" s="2" t="s">
+      <c r="E188" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F188" s="2" t="s">
+      <c r="F188" s="15" t="s">
         <v>18</v>
       </c>
       <c r="H188" s="2">
@@ -5626,13 +5644,13 @@
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A189" s="7">
+      <c r="A189" s="10">
         <v>549</v>
       </c>
-      <c r="E189" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F189" s="2" t="s">
+      <c r="E189" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F189" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H189" s="2">
@@ -5647,13 +5665,13 @@
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A190" s="7">
+      <c r="A190" s="10">
         <v>550</v>
       </c>
-      <c r="E190" s="2" t="s">
+      <c r="E190" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F190" s="2" t="s">
+      <c r="F190" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H190" s="2">
@@ -5668,13 +5686,13 @@
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A191" s="7">
+      <c r="A191" s="10">
         <v>551</v>
       </c>
-      <c r="E191" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F191" s="2" t="s">
+      <c r="E191" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F191" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H191" s="2">
@@ -5689,13 +5707,13 @@
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A192" s="7">
+      <c r="A192" s="10">
         <v>552</v>
       </c>
-      <c r="E192" s="2" t="s">
+      <c r="E192" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F192" s="2" t="s">
+      <c r="F192" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H192" s="2">
@@ -5710,13 +5728,13 @@
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A193" s="7">
+      <c r="A193" s="10">
         <v>553</v>
       </c>
-      <c r="E193" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F193" s="2" t="s">
+      <c r="E193" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F193" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H193" s="2">
@@ -5731,13 +5749,13 @@
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A194" s="7">
+      <c r="A194" s="10">
         <v>554</v>
       </c>
-      <c r="E194" s="2" t="s">
+      <c r="E194" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F194" s="2" t="s">
+      <c r="F194" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H194" s="2">
@@ -5752,13 +5770,13 @@
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A195" s="7">
+      <c r="A195" s="10">
         <v>555</v>
       </c>
-      <c r="E195" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F195" s="2" t="s">
+      <c r="E195" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F195" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H195" s="2">
@@ -5773,13 +5791,13 @@
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A196" s="7">
+      <c r="A196" s="10">
         <v>560</v>
       </c>
-      <c r="E196" s="2" t="s">
+      <c r="E196" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F196" s="2" t="s">
+      <c r="F196" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H196" s="2">
@@ -5794,13 +5812,13 @@
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A197" s="7">
+      <c r="A197" s="10">
         <v>563</v>
       </c>
-      <c r="E197" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F197" s="2" t="s">
+      <c r="E197" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F197" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H197" s="2">
@@ -5815,13 +5833,13 @@
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A198" s="7">
+      <c r="A198" s="10">
         <v>564</v>
       </c>
-      <c r="E198" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F198" s="2" t="s">
+      <c r="E198" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F198" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H198" s="2">
@@ -5836,13 +5854,13 @@
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A199" s="7">
+      <c r="A199" s="10">
         <v>565</v>
       </c>
-      <c r="E199" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F199" s="2" t="s">
+      <c r="E199" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F199" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H199" s="2">
@@ -5857,13 +5875,13 @@
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A200" s="7">
+      <c r="A200" s="10">
         <v>566</v>
       </c>
-      <c r="E200" s="2" t="s">
+      <c r="E200" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F200" s="2" t="s">
+      <c r="F200" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H200" s="2">
@@ -5878,13 +5896,13 @@
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A201" s="7">
+      <c r="A201" s="10">
         <v>567</v>
       </c>
-      <c r="E201" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F201" s="2" t="s">
+      <c r="E201" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F201" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H201" s="2">
@@ -5899,13 +5917,13 @@
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A202" s="7">
+      <c r="A202" s="10">
         <v>568</v>
       </c>
-      <c r="E202" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F202" s="2" t="s">
+      <c r="E202" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F202" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H202" s="2">
@@ -5920,13 +5938,13 @@
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A203" s="7">
+      <c r="A203" s="10">
         <v>569</v>
       </c>
-      <c r="E203" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F203" s="2" t="s">
+      <c r="E203" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F203" s="15" t="s">
         <v>17</v>
       </c>
       <c r="H203" s="2">
@@ -5941,13 +5959,13 @@
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A204" s="7">
+      <c r="A204" s="10">
         <v>570</v>
       </c>
-      <c r="E204" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F204" s="2" t="s">
+      <c r="E204" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F204" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H204" s="2">
@@ -5962,13 +5980,13 @@
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A205" s="7">
+      <c r="A205" s="10">
         <v>572</v>
       </c>
-      <c r="E205" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F205" s="2" t="s">
+      <c r="E205" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F205" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H205" s="2">
@@ -5983,13 +6001,13 @@
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A206" s="7">
+      <c r="A206" s="10">
         <v>573</v>
       </c>
-      <c r="E206" s="2" t="s">
+      <c r="E206" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F206" s="2" t="s">
+      <c r="F206" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H206" s="2">
@@ -6004,13 +6022,13 @@
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A207" s="7">
+      <c r="A207" s="10">
         <v>575</v>
       </c>
-      <c r="E207" s="2" t="s">
+      <c r="E207" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F207" s="2" t="s">
+      <c r="F207" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H207" s="2">
@@ -6025,13 +6043,13 @@
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A208" s="7">
+      <c r="A208" s="10">
         <v>576</v>
       </c>
-      <c r="E208" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F208" s="2" t="s">
+      <c r="E208" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F208" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H208" s="2">
@@ -6046,13 +6064,13 @@
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A209" s="7">
+      <c r="A209" s="10">
         <v>577</v>
       </c>
-      <c r="E209" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F209" s="2" t="s">
+      <c r="E209" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F209" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H209" s="2">
@@ -6067,13 +6085,13 @@
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A210" s="7">
+      <c r="A210" s="10">
         <v>578</v>
       </c>
-      <c r="E210" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F210" s="2" t="s">
+      <c r="E210" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F210" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H210" s="2">
@@ -6088,13 +6106,13 @@
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A211" s="7">
+      <c r="A211" s="10">
         <v>579</v>
       </c>
-      <c r="E211" s="2" t="s">
+      <c r="E211" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F211" s="2" t="s">
+      <c r="F211" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H211" s="2">
@@ -6109,13 +6127,13 @@
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A212" s="7">
+      <c r="A212" s="10">
         <v>580</v>
       </c>
-      <c r="E212" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F212" s="2" t="s">
+      <c r="E212" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F212" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H212" s="2">
@@ -6130,13 +6148,13 @@
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A213" s="7">
+      <c r="A213" s="10">
         <v>581</v>
       </c>
-      <c r="E213" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F213" s="2" t="s">
+      <c r="E213" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F213" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H213" s="2">
@@ -6151,13 +6169,13 @@
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A214" s="7">
+      <c r="A214" s="10">
         <v>583</v>
       </c>
-      <c r="E214" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F214" s="2" t="s">
+      <c r="E214" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F214" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H214" s="2">
@@ -6172,13 +6190,13 @@
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A215" s="7">
+      <c r="A215" s="10">
         <v>585</v>
       </c>
-      <c r="E215" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F215" s="2" t="s">
+      <c r="E215" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F215" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H215" s="2">
@@ -6193,13 +6211,13 @@
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A216" s="7">
+      <c r="A216" s="10">
         <v>586</v>
       </c>
-      <c r="E216" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F216" s="2" t="s">
+      <c r="E216" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F216" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H216" s="2">
@@ -6214,13 +6232,13 @@
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A217" s="7">
+      <c r="A217" s="10">
         <v>589</v>
       </c>
-      <c r="E217" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F217" s="2" t="s">
+      <c r="E217" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F217" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H217" s="2">
@@ -6235,13 +6253,13 @@
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A218" s="7">
+      <c r="A218" s="10">
         <v>590</v>
       </c>
-      <c r="E218" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F218" s="2" t="s">
+      <c r="E218" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F218" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H218" s="2">
@@ -6256,13 +6274,13 @@
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A219" s="7">
+      <c r="A219" s="10">
         <v>591</v>
       </c>
-      <c r="E219" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F219" s="2" t="s">
+      <c r="E219" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F219" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H219" s="2">
